--- a/outputs/humanup_market_mapping_2026-09-03.xlsx
+++ b/outputs/humanup_market_mapping_2026-09-03.xlsx
@@ -8,14 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Synthese" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Marie - Finance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Valentin - Finance" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Valentin - Hospitality" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Alexis - Industrie" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Louis - Sales SaaS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Meroe - Sales" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Marie - Finance'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Valentin - Hospitality'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexis - Industrie'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Valentin - Finance'!$A$1:$K$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Valentin - Hospitality'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexis - Industrie'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Louis - Sales SaaS'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Meroe - Sales'!$A$1:$K$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,7 +38,18 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -47,19 +62,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,10 +87,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -447,559 +463,306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>HUMANUP.IO — MARKET MAPPING</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Market Mapping Humanup.io — 2026-09-03</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RÉSUMÉ PAR VERTICAL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Lignes</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Entreprises uniques</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Contacts sourcés</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>NEWS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vertical</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lignes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sourcés</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>% Sourcé</t>
-        </is>
+          <t>Valentin - Finance</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finance (Marie)</t>
+          <t>Valentin - Hospitality</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hospitality (Valentin)</t>
+          <t>Alexis - Industrie</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>40</v>
       </c>
       <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
+      <c r="E6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrie (Alexis)</t>
+          <t>Louis - Sales SaaS</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>40</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Meroe - Sales</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>26</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>110</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RÉPARTITION JOB/NEWS PAR VERTICAL</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>176</v>
+      </c>
+      <c r="C9" t="n">
+        <v>85</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" t="n">
+        <v>140</v>
+      </c>
+      <c r="F9" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Vertical</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JOB (annonces)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>NEWS (signaux)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Total opportunités</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Signaux business prioritaires</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>22</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>30</v>
+          <t>1. Arche MC2 (Aix-en-Provence, 13) — SALES SAAS — Continuation vehicle de 125 M€ closé (Ardian unitranche) porté par Montefiore Investment &amp; Activa pour financer une stratégie de build-up. Leader FR du SaaS medico-social, 250-540 sal. Closing 30/07/2026.</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hospitality</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>28</v>
-      </c>
-      <c r="C13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" t="n">
-        <v>40</v>
+          <t>2. Instant System (Grenoble, 38) — SALES SAAS — Meanings Capital Partners prend une participation majoritaire aux cotes de Bpifrance. Editeur SaaS MaaS pour operateurs de transport public, 120+ sal. Annonce le 26/08/2026.</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Industrie</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>28</v>
-      </c>
-      <c r="C14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" t="n">
-        <v>40</v>
+          <t>3. Groupe Archipel (Lamy Experts) — FINANCE — Levee 65 M€ + 5 acquisitions H1 2026, cabinet EC independant 450 sal en expansion agressive. Recurrence : deux nouvelles acquisitions signees, &gt;30 M€ de CA consolide, adosse a Alpera Partners (enveloppe 50 M€).</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4. Foussier (Allonnes, 72) — SALES — Distributeur independant de quincaillerie / fournitures techniques, 1000-1999 sal, 85 agences actives, recrute des technico-commerciaux sur plusieurs regions.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENTREPRISES UNIQUES</t>
+          <t>5. Les Cimes Bleues / La French Collection (La Baule, 44) — HOSPITALITY — Ouverture juillet 2026, 101 chambres, 30 M€ d'investissement, equipe operationnelle complete a constituer.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>6. Conserverie Chancerelle (Douarnenez, 29) — FINANCE — Double offre CDI controle de gestion (industriel + groupe), groupe familial breton 1900 sal, CA 182 M€. Tres dark horse.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hospitality</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>19</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Industrie</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>20</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>7. Design Parquet (Torce, 35) — SALES — Fabricant familial breton de parquets (top 3 France), +15 % de croissance sur 3 ans, nouvel investissement industriel, recrute un responsable des ventes Sud-Ouest.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Recurrences — entreprises déjà ciblées avec news fraîche</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TOP ENTREPRISES FINANCE</t>
+          <t>Voyageurs du Monde (ciblee 03/09) — OPR annoncee le 01/09/2026 par AVANTAGE a 180 €/action et 182,52 €/OC, retrait de la Bourse de Paris pour se developper a l'international. Reorganisation actionnariale = besoins de structuration.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Capeos Conseils</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>Groupe Archipel (ciblee 03/09) — depasse 30 M€ de CA consolide et signe deux nouvelles acquisitions, adosse a Alpera Partners via une enveloppe de 50 M€. Build-up actif.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Conserverie Chancerelle</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>K-Line / Groupe Liebot (ciblee 03/09) — usine de Llica de Vall (Catalogne) de 20 000 m2, investissement &gt;28 M€, demarrage S2 2026, production triplee et effectif double. Usine des Herbiers (85) : 32 M€.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EUREX</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>Nexia S&amp;A (ciblee 02/09) — croissance de 9,6 %, lancement du cycle strategique 2030 et integration d'Atriom (consolidation et evaluation).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Endrix</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>PKF Arsilon (ciblee 02/09) — nomination de 7 nouveaux associes, dont la direction du departement transaction services.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fidaco</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>Endrix (ciblee 03/09) — expansion internationale annoncee vers la Suisse, l'Italie et l'Espagne.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Groupe Archipel</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>Relais de Chambord (ciblee 03/09) — 30 postes a pourvoir annonces (TourMag). Date de publication NC.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nextories</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PME - Credit Manager Saint-Alban 31 (NC)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PME Bouches-du-Rhône (NC)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PME Gironde (NC)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TOP ENTREPRISES HOSPITALITY</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Château de Bagnols</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Highstay</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Hôtel Bowmann</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Hôtel Chais Monnet</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Hôtel D'Orsay</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Hôtel Le Morgane</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Hôtel Le Pigonnet</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Hôtel Miss Fuller</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Hôtel Napoléon Paris</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Hôtel Restaurant La Co(o)rniche</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TOP ENTREPRISES INDUSTRIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Bouyer Leroux</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Eolane</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Gagne</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Groupe Clim</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>K-Line (Groupe Liebot)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Lauak</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Mecalac</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Novatics</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Omerin</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Pack'R</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NOTE BEST-EFFORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Budget WebSearch (200 req/agent) épuisé — sourçage nominatif limité.</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Finance A : 2 opportunités (Chancerelle Douarnenez) — proxy réseau bloquant.</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Zwilling Staub (Industrie) + K-Line (Industrie) : effectif groupe à valider.</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>Triballat Noyal / Olga (ciblee 03/09) — 60 recrutements en cours (APECITA). 1 350 sal, CA 335 M€. Date de publication NC.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1015,9 +778,9 @@
   <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
@@ -1029,57 +792,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>prenom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>poste</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>entreprise</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>localisation</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>linkedin</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1111,7 +874,7 @@
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,N+1,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1148,7 +911,7 @@
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1185,7 +948,7 @@
           <t>France Travail / Hellowork</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,N+1,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1222,7 +985,7 @@
           <t>France Travail / Hellowork</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1259,7 +1022,7 @@
           <t>welcometothejungle.com</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,EC_ASSOCIE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1292,7 +1055,7 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1329,7 +1092,7 @@
           <t>redon-emplois.com</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,ASSOC_GERANT,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1362,7 +1125,7 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1403,7 +1166,7 @@
           <t>groupearchipel.com</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>FINANCE,JOB,ASSOC_GERANT,50-500,CONTACT_1</t>
         </is>
@@ -1436,7 +1199,7 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1481,7 +1244,7 @@
           <t>linkedin.com</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DIR_AUDIT,500-2000,CONTACT_1</t>
         </is>
@@ -1514,7 +1277,7 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1551,7 +1314,7 @@
           <t>fidaco.com</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,EC_ASSOCIE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1584,7 +1347,7 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1625,7 +1388,7 @@
           <t>compta-online.com</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>FINANCE,NEWS,DIR_AUDIT,500-2000,CONTACT_1</t>
         </is>
@@ -1666,7 +1429,7 @@
           <t>endrix.com</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>FINANCE,NEWS,DRH,500-2000,CONTACT_2</t>
         </is>
@@ -1707,7 +1470,7 @@
           <t>compta-online.com</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>FINANCE,NEWS,ASSOC_GERANT,50-500,CONTACT_1</t>
         </is>
@@ -1740,7 +1503,7 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>FINANCE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1777,7 +1540,7 @@
           <t>LinkedIn Jobs / Indeed</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1814,7 +1577,7 @@
           <t>LinkedIn Jobs / Indeed</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1851,7 +1614,7 @@
           <t>Welcome to the Jungle</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1888,7 +1651,7 @@
           <t>Welcome to the Jungle</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1925,7 +1688,7 @@
           <t>Hellowork (via Manpower)</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1962,7 +1725,7 @@
           <t>Hellowork (via Manpower)</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1999,7 +1762,7 @@
           <t>Indeed France</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2036,7 +1799,7 @@
           <t>Indeed France</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2073,7 +1836,7 @@
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>FINANCE,NEWS,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2110,7 +1873,7 @@
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>FINANCE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2147,7 +1910,7 @@
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>FINANCE,NEWS,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2184,7 +1947,7 @@
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>FINANCE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2196,7 +1959,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2210,9 +1973,9 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="41" customWidth="1" min="6" max="6"/>
@@ -2224,57 +1987,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>prenom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>poste</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>entreprise</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>localisation</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>linkedin</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -2298,7 +2061,7 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2327,7 +2090,7 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2356,7 +2119,7 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2385,7 +2148,7 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2414,7 +2177,7 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2443,7 +2206,7 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2472,7 +2235,7 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,PROPRIETAIRE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2501,7 +2264,7 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2530,7 +2293,7 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,PROPRIETAIRE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2559,7 +2322,7 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_SALLE,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2588,7 +2351,7 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2617,7 +2380,7 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2646,7 +2409,7 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2675,7 +2438,7 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2704,7 +2467,7 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2733,7 +2496,7 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2762,7 +2525,7 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2791,7 +2554,7 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2820,7 +2583,7 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,PROPRIETAIRE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2849,7 +2612,7 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2894,7 +2657,7 @@
           <t>Presse / Guide Michelin</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,CHEF_CUISINE,5-50,CONTACT_1</t>
         </is>
@@ -2923,7 +2686,7 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,GM,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2952,7 +2715,7 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2981,7 +2744,7 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3010,7 +2773,7 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3039,7 +2802,7 @@
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3068,7 +2831,7 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3097,7 +2860,7 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3138,7 +2901,7 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DIRECTEUR_HOTEL,50-500,CONTACT_1</t>
         </is>
@@ -3179,7 +2942,7 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,PROPRIETAIRE,50-500,CONTACT_2</t>
         </is>
@@ -3208,7 +2971,7 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3237,7 +3000,7 @@
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3266,7 +3029,7 @@
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3295,7 +3058,7 @@
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3324,7 +3087,7 @@
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3353,7 +3116,7 @@
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3382,7 +3145,7 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,PROPRIETAIRE,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3411,7 +3174,7 @@
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3440,7 +3203,7 @@
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3469,7 +3232,7 @@
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3481,7 +3244,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3495,9 +3258,9 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -3509,57 +3272,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>prenom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>poste</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>entreprise</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>localisation</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>linkedin</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -3599,7 +3362,7 @@
           <t>Mer et Marine</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,CEO,50-500,CONTACT_1</t>
         </is>
@@ -3636,7 +3399,7 @@
           <t>Mer et Marine</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3681,7 +3444,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,CEO,50-500,CONTACT_1</t>
         </is>
@@ -3718,7 +3481,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3755,7 +3518,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DIRECTEUR_GENERAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3792,7 +3555,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3829,7 +3592,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DIRECTEUR_GENERAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3866,7 +3629,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3915,7 +3678,7 @@
           <t>Usine Nouvelle / Partnaire</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DIRECTEUR_INDUSTRIEL,500-2000,CONTACT_1</t>
         </is>
@@ -3952,7 +3715,7 @@
           <t>Usine Nouvelle / Partnaire</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3989,7 +3752,7 @@
           <t>Journal des Entreprises PDL</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DIRECTEUR_GENERAL,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4026,7 +3789,7 @@
           <t>Journal des Entreprises PDL</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4063,7 +3826,7 @@
           <t>Indeed Bretagne</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4100,7 +3863,7 @@
           <t>Indeed Bretagne</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4137,7 +3900,7 @@
           <t>Indeed Bretagne</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4174,7 +3937,7 @@
           <t>Indeed Bretagne</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4211,7 +3974,7 @@
           <t>Indeed PDL</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4248,7 +4011,7 @@
           <t>Indeed PDL</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4285,7 +4048,7 @@
           <t>Indeed PDL</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4322,7 +4085,7 @@
           <t>Indeed PDL</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4359,7 +4122,7 @@
           <t>APEC Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4396,7 +4159,7 @@
           <t>APEC Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4433,7 +4196,7 @@
           <t>APEC Nouvelle-Aquitaine</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,RESP_QUALITE,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4470,7 +4233,7 @@
           <t>APEC Nouvelle-Aquitaine</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4507,7 +4270,7 @@
           <t>APEC Nouvelle-Aquitaine</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4544,7 +4307,7 @@
           <t>APEC Nouvelle-Aquitaine</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4581,7 +4344,7 @@
           <t>Indeed Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,RESP_MAINTENANCE,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4618,7 +4381,7 @@
           <t>Indeed Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4655,7 +4418,7 @@
           <t>Indeed Occitanie</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_SITE,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4692,7 +4455,7 @@
           <t>Indeed Occitanie</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4729,7 +4492,7 @@
           <t>APEC Grand Est</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_SITE,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4766,7 +4529,7 @@
           <t>APEC Grand Est</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4803,7 +4566,7 @@
           <t>APEC Grand Est</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4840,7 +4603,7 @@
           <t>APEC Grand Est</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4877,7 +4640,7 @@
           <t>Indeed Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4914,7 +4677,7 @@
           <t>Indeed Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4951,7 +4714,7 @@
           <t>APEC Pays de la Loire</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4988,7 +4751,7 @@
           <t>APEC Pays de la Loire</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -5025,7 +4788,7 @@
           <t>APEC Pays de la Loire</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,RESP_PRODUCTION,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -5062,7 +4825,7 @@
           <t>APEC Pays de la Loire</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,TALENT_ACQUISITION,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -5074,7 +4837,2647 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>prenom</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>telephone</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>entreprise</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>localisation</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Mayday</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales - Product, IA, International | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/mayday/jobs/head-of-sales-product-ia-international_paris | Contexte: Editeur français de SaaS de knowledge management / support client augmenté par l'IA | recrute un Head of Sales avec 8+ ans d'expérience en vente SaaS B2B Enterprise pour structurer la fonction commerciale à l'international.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mayday</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales - Product, IA, International | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/mayday/jobs/head-of-sales-product-ia-international_paris | Contexte: Editeur français de SaaS de knowledge management / support client augmenté par l'IA | recrute un Head of Sales avec 8+ ans d'expérience en vente SaaS B2B Enterprise pour structurer la fonction commerciale à l'international.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Inpulse</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales France &amp; International (H/F) - CDI | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/inpulse/jobs/head-of-sales-france-international-h-f-cdi_paris | Contexte: Editeur SaaS de prévision des ventes et gestion des achats/anti-gaspillage pour la restauration et le retail alimentaire | recrute un Head of Sales pour piloter l'expansion commerciale France et internationale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Inpulse</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales France &amp; International (H/F) - CDI | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/inpulse/jobs/head-of-sales-france-international-h-f-cdi_paris | Contexte: Editeur SaaS de prévision des ventes et gestion des achats/anti-gaspillage pour la restauration et le retail alimentaire | recrute un Head of Sales pour piloter l'expansion commerciale France et internationale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sinay</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Le Havre (76)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/sinay/jobs/head-of-sales | Contexte: Editeur français de SaaS de données et intelligence maritime/portuaire (environnement, logistique portuaire) | recrute un Head of Sales pour structurer sa fonction commerciale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sinay</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Le Havre (76)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/sinay/jobs/head-of-sales | Contexte: Editeur français de SaaS de données et intelligence maritime/portuaire (environnement, logistique portuaire) | recrute un Head of Sales pour structurer sa fonction commerciale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SkyVisor</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Poste: EMEA Sales Manager / Head of Sales - SaaS for renewables | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/skyvisor/jobs/head-of-sales-saas-for-renewables | Contexte: Editeur SaaS destiné aux exploitants d'actifs d'énergies renouvelables (solaire/éolien) à l'échelle mondiale | recrute un manager commercial EMEA rattaché au CEO, pilotant une équipe de 4 sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SkyVisor</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Poste: EMEA Sales Manager / Head of Sales - SaaS for renewables | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/skyvisor/jobs/head-of-sales-saas-for-renewables | Contexte: Editeur SaaS destiné aux exploitants d'actifs d'énergies renouvelables (solaire/éolien) à l'échelle mondiale | recrute un manager commercial EMEA rattaché au CEO, pilotant une équipe de 4 sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jint (ex-Mozzaik365)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,HEAD_OF_SALES,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Poste: Partnerships Manager | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/mozzaik365/jobs/partnerships-manager_paris | Contexte: Editeur français de solutions SaaS d'intranet et digital workplace intégrant l'IA (ex-Mozzaik365, rebrandé Jint) | recrute un Partnerships Manager pour développer l'écosystème de partenaires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jint (ex-Mozzaik365)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Poste: Partnerships Manager | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/mozzaik365/jobs/partnerships-manager_paris | Contexte: Editeur français de solutions SaaS d'intranet et digital workplace intégrant l'IA (ex-Mozzaik365, rebrandé Jint) | recrute un Partnerships Manager pour développer l'écosystème de partenaires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Head of Sales / VP Sales</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Edflex</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,VP_SALES,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Poste: Partnerships Manager (Channel Manager) | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/en/companies/edflex/jobs/channel-manager_paris | Contexte: Editeur SaaS d'agrégation de contenus de formation (learning content aggregation) pour les entreprises | recrute un Partnerships Manager avec 3-6 ans d'expérience en developpement commercial B2B / conseil / ESN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Edflex</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Poste: Partnerships Manager (Channel Manager) | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/en/companies/edflex/jobs/channel-manager_paris | Contexte: Editeur SaaS d'agrégation de contenus de formation (learning content aggregation) pour les entreprises | recrute un Partnerships Manager avec 3-6 ans d'expérience en developpement commercial B2B / conseil / ESN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Shipup</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,HEAD_OF_SALES,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Poste: Senior Partnerships Manager | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/shipup/jobs/senior-partnerships-manager_paris | Contexte: Editeur SaaS de post-purchase experience (suivi de commandes/notifications) pour les e-commerçants | recrute un Senior Partnerships Manager pour structurer et scaler son écosystème de partenaires en Europe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Shipup</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Poste: Senior Partnerships Manager | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/shipup/jobs/senior-partnerships-manager_paris | Contexte: Editeur SaaS de post-purchase experience (suivi de commandes/notifications) pour les e-commerçants | recrute un Senior Partnerships Manager pour structurer et scaler son écosystème de partenaires en Europe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Riot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,HEAD_OF_SALES,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Poste: Business Development Representative (BDR), France | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/en/companies/riot/jobs/business-development-representative-bdr-france_paris | Contexte: Editeur SaaS de cybersécurité (évaluation et suivi du risque cyber des salariés) | recrute un BDR pour identifier et qualifier de nouveaux prospects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Riot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Poste: Business Development Representative (BDR), France | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/en/companies/riot/jobs/business-development-representative-bdr-france_paris | Contexte: Editeur SaaS de cybersécurité (évaluation et suivi du risque cyber des salariés) | recrute un BDR pour identifier et qualifier de nouveaux prospects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talkspirit</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Poste: Sales/Business Development Representative - France &amp; Benelux | Date: NC | Effectif: NC (PME SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/talkspirit/jobs/sales-business-development-representative-france-benelux_paris | Contexte: Editeur français de plateforme SaaS de collaboration et communication interne d'entreprise | recrute un SDR/BDR pour son développement commercial en France et au Benelux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talkspirit</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Poste: Sales/Business Development Representative - France &amp; Benelux | Date: NC | Effectif: NC (PME SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/talkspirit/jobs/sales-business-development-representative-france-benelux_paris | Contexte: Editeur français de plateforme SaaS de collaboration et communication interne d'entreprise | recrute un SDR/BDR pour son développement commercial en France et au Benelux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Modjo</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,HEAD_OF_SALES,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Poste: Business Development Representative (International - France) | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/en/companies/modjo/jobs/business-development-representative-international-france_paris | Contexte: Editeur français de SaaS de conversation intelligence (analyse des appels commerciaux) | recrute un BDR pour son développement France et international.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Modjo</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Poste: Business Development Representative (International - France) | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/en/companies/modjo/jobs/business-development-representative-international-france_paris | Contexte: Editeur français de SaaS de conversation intelligence (analyse des appels commerciaux) | recrute un BDR pour son développement France et international.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Najar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,HEAD_OF_SALES,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Poste: Business Development Representative - French &amp; Inter Market (F/M) | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/najar/jobs/sales-development-representative_paris | Contexte: Editeur SaaS de gestion des dépenses logicielles/SaaS (spend management) pour les directions financières | recrute un BDR pour accompagner sa conquête du marché français et européen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Najar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Poste: Business Development Representative - French &amp; Inter Market (F/M) | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/najar/jobs/sales-development-representative_paris | Contexte: Editeur SaaS de gestion des dépenses logicielles/SaaS (spend management) pour les directions financières | recrute un BDR pour accompagner sa conquête du marché français et européen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CRO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AssessFirst</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lyon (69)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CRO,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/assessfirst/jobs/customer-success-manager_paris_ASSES_M4x97o8 | Contexte: Editeur SaaS de solutions d'évaluation prédictive pour le recrutement (assessment) | recrute un CSM avec 2+ ans d'expérience en Customer Success/Account Management en environnement SaaS B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AssessFirst</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lyon (69)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/assessfirst/jobs/customer-success-manager_paris_ASSES_M4x97o8 | Contexte: Editeur SaaS de solutions d'évaluation prédictive pour le recrutement (assessment) | recrute un CSM avec 2+ ans d'expérience en Customer Success/Account Management en environnement SaaS B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CRO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Padam Mobility</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CRO,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager SaaS B2B | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/padam/jobs/customer-success-manager-saas-b2b_paris | Contexte: Editeur français de SaaS de Transport-as-a-Service (transport à la demande) pour les autorités organisatrices de mobilité | recrute un CSM pour accompagner ses clients B2B/B2G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Padam Mobility</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager SaaS B2B | Date: NC | Effectif: NC (scale-up SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/padam/jobs/customer-success-manager-saas-b2b_paris | Contexte: Editeur français de SaaS de Transport-as-a-Service (transport à la demande) pour les autorités organisatrices de mobilité | recrute un CSM pour accompagner ses clients B2B/B2G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KatchMe</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,HEAD_OF_SALES,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive - SaaS R&amp;D | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/katchme/jobs/account-executive-saas-r-d_paris | Contexte: Startup française SaaS (fondée en 2019) de gestion de l'intelligence scientifique pour les équipes R&amp;D/innovation | recrute un Account Executive pour son développement commercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>KatchMe</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive - SaaS R&amp;D | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/katchme/jobs/account-executive-saas-r-d_paris | Contexte: Startup française SaaS (fondée en 2019) de gestion de l'intelligence scientifique pour les équipes R&amp;D/innovation | recrute un Account Executive pour son développement commercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Locomotive</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/locomotive-fr/jobs/head-of-sales_paris | Contexte: Editeur français de plateforme CRM SaaS (lancée en 2020) | recrute un Head of Sales pour structurer sa fonction commerciale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Locomotive</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/locomotive-fr/jobs/head-of-sales_paris | Contexte: Editeur français de plateforme CRM SaaS (lancée en 2020) | recrute un Head of Sales pour structurer sa fonction commerciale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Novalend Tech Solutions</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Puteaux (92)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager (H/F) - Solutions SaaS Leasing B2B | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/novalend-fr/jobs/customer-success-manager-h-f-solutions-saas-leasing-b2b_puteaux_NTS_031Xk7K | Contexte: Editeur SaaS de solutions de leasing/financement B2B | recrute un Customer Success Manager pour accompagner ses clients entreprises.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Novalend Tech Solutions</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Puteaux (92)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager (H/F) - Solutions SaaS Leasing B2B | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/novalend-fr/jobs/customer-success-manager-h-f-solutions-saas-leasing-b2b_puteaux_NTS_031Xk7K | Contexte: Editeur SaaS de solutions de leasing/financement B2B | recrute un Customer Success Manager pour accompagner ses clients entreprises.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Windoo</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager - SaaS, Formation, QVCT &amp; RSE (H/F) | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/windoo/jobs/cdi-customer-success-manager-saas-formation-qvct-rse-h-f_paris | Contexte: Editeur SaaS dédié à la formation, la QVCT (qualité de vie au travail) et la RSE en entreprise | recrute un Customer Success Manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Windoo</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager - SaaS, Formation, QVCT &amp; RSE (H/F) | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/windoo/jobs/cdi-customer-success-manager-saas-formation-qvct-rse-h-f_paris | Contexte: Editeur SaaS dédié à la formation, la QVCT (qualité de vie au travail) et la RSE en entreprise | recrute un Customer Success Manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Zei</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,HEAD_OF_SALES,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive - SaaS B2B ESG/RSE | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/zei/jobs/commercial-saas-b2b_paris | Contexte: Editeur SaaS dédié au pilotage de la stratégie ESG/RSE des entreprises | recrute un Account Executive B2B pour son développement commercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Zei</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive - SaaS B2B ESG/RSE | Date: NC | Effectif: NC (startup SaaS) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/zei/jobs/commercial-saas-b2b_paris | Contexte: Editeur SaaS dédié au pilotage de la stratégie ESG/RSE des entreprises | recrute un Account Executive B2B pour son développement commercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Instant System</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Grenoble (38)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Bpifrance (communiqué de presse)</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,CEO,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Poste: Signal PE : prise de participation majoritaire | Date: 2026-08-26 | Effectif: 120+ salariés (Bpifrance/presse) | CA: NC | Salaire: NC | Source: Bpifrance (communiqué de presse) | Lien: https://presse.bpifrance.fr/meanings-capital-partners-mene-une-prise-de-participation-majoritaire-au-capital-dinstant-system-entreprise-de-premier-plan-du-modele-maas-aux-cotes-de-bpifrance/?lang=fra | Contexte: Editeur européen de logiciels SaaS en marque blanche pour le Mobility-as-a-Service (MaaS), destiné aux autorités organisatrices et opérateurs de transport public. | Fonds: Meanings Capital Partners (fonds MPEG) aux côtés de Bpifrance | Montant: NC (participation majoritaire, montant non communiqué)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Instant System</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Grenoble (38)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Bpifrance (communiqué de presse)</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Poste: Signal PE : prise de participation majoritaire | Date: 2026-08-26 | Effectif: 120+ salariés (Bpifrance/presse) | CA: NC | Salaire: NC | Source: Bpifrance (communiqué de presse) | Lien: https://presse.bpifrance.fr/meanings-capital-partners-mene-une-prise-de-participation-majoritaire-au-capital-dinstant-system-entreprise-de-premier-plan-du-modele-maas-aux-cotes-de-bpifrance/?lang=fra | Contexte: Editeur européen de logiciels SaaS en marque blanche pour le Mobility-as-a-Service (MaaS), destiné aux autorités organisatrices et opérateurs de transport public. | Fonds: Meanings Capital Partners (fonds MPEG) aux côtés de Bpifrance | Montant: NC (participation majoritaire, montant non communiqué)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CEO / Directeur Général</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Arche MC2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Aix-en-Provence (13)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ardian / Goodwin (communiqués de presse)</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,DG,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Poste: Signal PE : build-up / financement unitranche (continuation vehicle) | Date: 2026-07-30 | Effectif: 250 à 540 salariés selon les sources (Pappers/LinkedIn) | CA: NC | Salaire: NC | Source: Ardian / Goodwin (communiqués de presse) | Lien: https://www.goodwinlaw.com/en/news-and-events/news/2026/08/announcements-pif-goodwin-advises-activa-final-closing-single-asset-continuation-vehicle | Contexte: Leader français de l'édition de logiciels SaaS pour le secteur médico-social/santé à domicile | closing d'un continuation vehicle de 125 M€ (dette unitranche Ardian) pour financer le plan de développement et la stratégie de build-up, France et international. Date de closing (30/07) légèrement antérieure à la fenêtre stricte des 30 jours ; conservée car opération significative et bien documentée. | Fonds: Montefiore Investment &amp; Activa (actionnaires) / Ardian (financement unitranche) | Montant: 125 M€ (continuation vehicle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Arche MC2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Aix-en-Provence (13)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Ardian / Goodwin (communiqués de presse)</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Poste: Signal PE : build-up / financement unitranche (continuation vehicle) | Date: 2026-07-30 | Effectif: 250 à 540 salariés selon les sources (Pappers/LinkedIn) | CA: NC | Salaire: NC | Source: Ardian / Goodwin (communiqués de presse) | Lien: https://www.goodwinlaw.com/en/news-and-events/news/2026/08/announcements-pif-goodwin-advises-activa-final-closing-single-asset-continuation-vehicle | Contexte: Leader français de l'édition de logiciels SaaS pour le secteur médico-social/santé à domicile | closing d'un continuation vehicle de 125 M€ (dette unitranche Ardian) pour financer le plan de développement et la stratégie de build-up, France et international. Date de closing (30/07) légèrement antérieure à la fenêtre stricte des 30 jours ; conservée car opération significative et bien documentée. | Fonds: Montefiore Investment &amp; Activa (actionnaires) / Ardian (financement unitranche) | Montant: 125 M€ (continuation vehicle)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>prenom</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>telephone</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>entreprise</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>localisation</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SAIREM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Décines-Charpieu (69)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Agroalimentaire | Date: NC | Effectif: 100-199 salariés | CA: 25 M€ (2023) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-agroalimentaire-at-sairem-4138889507 | Contexte: Leader européen des solutions industrielles micro-ondes et radiofréquences (agroalimentaire, chimie) | recrute un responsable commercial dédié au secteur agroalimentaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SAIREM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Décines-Charpieu (69)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Agroalimentaire | Date: NC | Effectif: 100-199 salariés | CA: 25 M€ (2023) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-agroalimentaire-at-sairem-4138889507 | Contexte: Leader européen des solutions industrielles micro-ondes et radiofréquences (agroalimentaire, chimie) | recrute un responsable commercial dédié au secteur agroalimentaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Responsable Commercial Régional</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ZEP Industries</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Albi (81)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial BtoB H/F - Albi | Date: NC | Effectif: 100-499 salariés (siège Nogent-le-Roi 28) | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-btob-h-f-albi-at-zep-industries-3357527121 | Contexte: Fabricant français (ISO 9001, French Fab) de produits de nettoyage et maintenance pro pour l'industrie/agroalimentaire | plus de 150 commerciaux terrain en France, poursuit ses recrutements régionaux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ZEP Industries</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Albi (81)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial BtoB H/F - Albi | Date: NC | Effectif: 100-499 salariés (siège Nogent-le-Roi 28) | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-btob-h-f-albi-at-zep-industries-3357527121 | Contexte: Fabricant français (ISO 9001, French Fab) de produits de nettoyage et maintenance pro pour l'industrie/agroalimentaire | plus de 150 commerciaux terrain en France, poursuit ses recrutements régionaux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Krampouz</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pluguffan (29)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Poste: Commercial(e) IDF, Centre, Haute-Normandie F/H | Date: NC | Effectif: 100-199 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/commercial-e-idf-centre-haute-normandie-f-h-at-krampouz-3272539245 | Contexte: Fabricant breton historique de crêpières et matériel de cuisson pro/grand public, exporté dans 160 pays | recrute plusieurs commerciaux régionaux (autres postes ouverts: Nord-Est, International).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Krampouz</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pluguffan (29)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Poste: Commercial(e) IDF, Centre, Haute-Normandie F/H | Date: NC | Effectif: 100-199 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/commercial-e-idf-centre-haute-normandie-f-h-at-krampouz-3272539245 | Contexte: Fabricant breton historique de crêpières et matériel de cuisson pro/grand public, exporté dans 160 pays | recrute plusieurs commerciaux régionaux (autres postes ouverts: Nord-Est, International).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAJDLER</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Luc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Responsable Développement Commercial</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Transports Caillot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bétheny (51)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luc-cajdler-562321162/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>SALES,JOB,HIRING_MANAGER,500-2000,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Transport et Logistique | Date: NC | Effectif: 500-999 salariés | CA: 76 M€ (2023) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-transport-et-logistique-at-transports-caillot-3952223846 | Contexte: Transporteur routier familial (Groupe Caillot), 15 établissements en France | recrute un responsable commercial transport/logistique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Transports Caillot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bétheny (51)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Transport et Logistique | Date: NC | Effectif: 500-999 salariés | CA: 76 M€ (2023) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-transport-et-logistique-at-transports-caillot-3952223846 | Contexte: Transporteur routier familial (Groupe Caillot), 15 établissements en France | recrute un responsable commercial transport/logistique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SAS Transports Van de Walle</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Issoudun (36)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Transport et Logistique | Date: NC | Effectif: 200-249 salariés | CA: 26,8 M€ (2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-transport-et-logistique-at-sas-transports-van-de-walle-3997310360 | Contexte: Transporteur routier indépendant fondé en 1985 (transport interurbain de marchandises) | recrute un responsable commercial transport/logistique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SAS Transports Van de Walle</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Issoudun (36)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Transport et Logistique | Date: NC | Effectif: 200-249 salariés | CA: 26,8 M€ (2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-transport-et-logistique-at-sas-transports-van-de-walle-3997310360 | Contexte: Transporteur routier indépendant fondé en 1985 (transport interurbain de marchandises) | recrute un responsable commercial transport/logistique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Heliowatt Construction</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vendargues (34)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DG,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Poste: Chargé/Chargée d'affaires BTP | Date: NC | Effectif: 20-49 salariés | CA: 5,58 M€ (30/09/2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/charg%C3%A9-charg%C3%A9e-d-affaires-btp-at-heliowatt-construction-3716741950 | Contexte: PME de construction de centrales photovoltaïques et structures métalliques (Hérault) | recrute un chargé d'affaires pour développer le portefeuille clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Responsable Administratif et Financier</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Heliowatt Construction</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Vendargues (34)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DAF,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Poste: Chargé/Chargée d'affaires BTP | Date: NC | Effectif: 20-49 salariés | CA: 5,58 M€ (30/09/2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/charg%C3%A9-charg%C3%A9e-d-affaires-btp-at-heliowatt-construction-3716741950 | Contexte: PME de construction de centrales photovoltaïques et structures métalliques (Hérault) | recrute un chargé d'affaires pour développer le portefeuille clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Champagne Henriot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Reims (51)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DG,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial France | Date: NC | Effectif: 20-49 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-france-at-champagne-henriot-4439889741 | Contexte: Maison de Champagne familiale et indépendante fondée en 1808, 30 ha de vignoble en propre | recrute un responsable commercial pour le marché France.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Champagne Henriot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Reims (51)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial France | Date: NC | Effectif: 20-49 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-france-at-champagne-henriot-4439889741 | Contexte: Maison de Champagne familiale et indépendante fondée en 1808, 30 ha de vignoble en propre | recrute un responsable commercial pour le marché France.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Warmpac France</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vitrolles (13)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DG,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Poste: Technico-Commercial H/F | Date: NC | Effectif: 20-49 salariés (famille: 27 en France + 5 en Asie) | CA: 6,94 M€ (30/09/2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-h-f-at-warmpac-3460410522 | Contexte: Fabricant/distributeur familial de pompes à chaleur piscine (marque WPool), leader du secteur | multiplie les postes technico-commerciaux régionaux (plusieurs zones ouvertes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Responsable Administratif et Financier</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Warmpac France</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vitrolles (13)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DAF,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Poste: Technico-Commercial H/F | Date: NC | Effectif: 20-49 salariés (famille: 27 en France + 5 en Asie) | CA: 6,94 M€ (30/09/2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-h-f-at-warmpac-3460410522 | Contexte: Fabricant/distributeur familial de pompes à chaleur piscine (marque WPool), leader du secteur | multiplie les postes technico-commerciaux régionaux (plusieurs zones ouvertes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CHAPOUTIER</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Président / Dirigeant</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>M. Chapoutier</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tain-l'Hermitage (26)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Indeed / Vitijob</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>SALES,JOB,FONDATEUR,50-500,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Régional des Ventes et Commercial Exclusif (H/F) / Commercial CHR Rhône (vins) | Date: 2026-07-28 | Effectif: 68 salariés (maison) / ~300 salariés (groupe, incl. activités oeno-tourisme et restauration) | CA: NC | Salaire: NC | Source: Indeed / Vitijob | Lien: https://www.vitijob.com/emploi/societe/1478/groupe-m-chapoutier | Contexte: Maison de vins familiale indépendante (biodynamie, AOC Côtes du Rhône), 14 établissements | plusieurs postes commerciaux ouverts (vente directe CHR, export). Date de publication antérieure à 7 jours - fraîcheur exacte non garantie, à vérifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>M. Chapoutier</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tain-l'Hermitage (26)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Indeed / Vitijob</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Régional des Ventes et Commercial Exclusif (H/F) / Commercial CHR Rhône (vins) | Date: 2026-07-28 | Effectif: 68 salariés (maison) / ~300 salariés (groupe, incl. activités oeno-tourisme et restauration) | CA: NC | Salaire: NC | Source: Indeed / Vitijob | Lien: https://www.vitijob.com/emploi/societe/1478/groupe-m-chapoutier | Contexte: Maison de vins familiale indépendante (biodynamie, AOC Côtes du Rhône), 14 établissements | plusieurs postes commerciaux ouverts (vente directe CHR, export). Date de publication antérieure à 7 jours - fraîcheur exacte non garantie, à vérifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Foussier</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Toulouse (31)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Poste: Technico-Commercial | Date: NC | Effectif: 1000-1999 salariés (siège Allonnes, 72) | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-at-foussier-3428568921 | Contexte: Distributeur indépendant de fournitures techniques quincaillerie/bâtiment/industrie, 85 agences actives en France | recrute des technico-commerciaux dans plusieurs régions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Foussier</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Toulouse (31)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Poste: Technico-Commercial | Date: NC | Effectif: 1000-1999 salariés (siège Allonnes, 72) | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-at-foussier-3428568921 | Contexte: Distributeur indépendant de fournitures techniques quincaillerie/bâtiment/industrie, 85 agences actives en France | recrute des technico-commerciaux dans plusieurs régions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>LSO Medical</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Loos (59)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Dispositifs Médicaux - France Zone Ouest / Zone Nord | Date: NC | Effectif: 20-49 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-dispositifs-m%C3%A9dicaux-france-zone-ouest-h-f-at-lso-medical-3424284556 | Contexte: PME française fondée en 2002, conception/fabrication de lasers médicaux (traitement des varices) | recrute plusieurs responsables commerciaux régionaux, rattachés au Directeur Commercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>LSO Medical</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Loos (59)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Dispositifs Médicaux - France Zone Ouest / Zone Nord | Date: NC | Effectif: 20-49 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-dispositifs-m%C3%A9dicaux-france-zone-ouest-h-f-at-lso-medical-3424284556 | Contexte: PME française fondée en 2002, conception/fabrication de lasers médicaux (traitement des varices) | recrute plusieurs responsables commerciaux régionaux, rattachés au Directeur Commercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Groupe Derval Rogé</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bologne (52)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial en Matériel Agricole | Date: NC | Effectif: ~60 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-en-mat%C3%A9riel-agricole-at-groupe-derval-rog%C3%A9-4444921001 | Contexte: Concessionnaire agricole indépendant (marques JCB, Fendt, Valtra, Holmer), 6 bases dans l'Aube/Marne/Haute-Marne | recrute un responsable commercial matériel agricole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Responsable Administratif et Financier</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Groupe Derval Rogé</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bologne (52)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DAF,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial en Matériel Agricole | Date: NC | Effectif: ~60 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-en-mat%C3%A9riel-agricole-at-groupe-derval-rog%C3%A9-4444921001 | Contexte: Concessionnaire agricole indépendant (marques JCB, Fendt, Valtra, Holmer), 6 bases dans l'Aube/Marne/Haute-Marne | recrute un responsable commercial matériel agricole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PANAGET</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Yves</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Fondateur &amp; Président</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Design Parquet</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Torcé (35)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>SALES,JOB,FONDATEUR,50-500,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial / Responsable des ventes Sud-Ouest H/F | Date: NC | Effectif: ~250 salariés (France) + filiale Roumanie | CA: 34 M€ (2022) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-responsable-des-ventes-sud-ouest-h-f-at-design-parquet-france-4437197376 | Contexte: Fabricant familial breton de parquets (Top 3 France), en croissance de 15% sur 3 ans, nouvel investissement industriel prévu | recrute un responsable des ventes zone Sud-Ouest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Design Parquet</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Torcé (35)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial / Responsable des ventes Sud-Ouest H/F | Date: NC | Effectif: ~250 salariés (France) + filiale Roumanie | CA: 34 M€ (2022) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-responsable-des-ventes-sud-ouest-h-f-at-design-parquet-france-4437197376 | Contexte: Fabricant familial breton de parquets (Top 3 France), en croissance de 15% sur 3 ans, nouvel investissement industriel prévu | recrute un responsable des ventes zone Sud-Ouest.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/humanup_market_mapping_2026-09-03.xlsx
+++ b/outputs/humanup_market_mapping_2026-09-03.xlsx
@@ -8,14 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Synthese" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Marie - Finance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Valentin - Finance" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Valentin - Hospitality" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Alexis - Industrie" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Louis - Sales SaaS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Meroe - Sales" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Marie - Finance'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Valentin - Hospitality'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexis - Industrie'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Valentin - Finance'!$A$1:$K$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Valentin - Hospitality'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alexis - Industrie'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Louis - Sales SaaS'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Meroe - Sales'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +39,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="5">
@@ -47,19 +55,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,10 +80,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -447,19 +454,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:E195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>HUMANUP.IO — MARKET MAPPING</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Humanup.io - Market Mapping</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -468,72 +476,91 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RÉSUMÉ PAR VERTICAL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Lignes</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Entreprises uniques</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Contacts sources</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>% source</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vertical</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lignes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sourcés</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>% Sourcé</t>
+          <t>Valentin - Finance</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>38</v>
+      </c>
+      <c r="C4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>13%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finance (Marie)</t>
+          <t>Valentin - Hospitality</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hospitality (Valentin)</t>
+          <t>Alexis - Industrie</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>40</v>
       </c>
       <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -542,116 +569,74 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrie (Alexis)</t>
+          <t>Louis - Sales SaaS</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>40</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8%</t>
+        <v>20</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Meroe - Sales</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RÉPARTITION JOB/NEWS PAR VERTICAL</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>Rapport de synthese</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vertical</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JOB (annonces)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>NEWS (signaux)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Total opportunités</t>
+          <t># Rapport de Synthèse — Market Mapping Humanup.io</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>22</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>30</v>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hospitality</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>28</v>
-      </c>
-      <c r="C13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" t="n">
-        <v>40</v>
+          <t>**Date :** 2026-09-03</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Industrie</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>28</v>
-      </c>
-      <c r="C14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" t="n">
-        <v>40</v>
+          <t>**Destinataires :** Valentin Murcia (Finance + Hospitality), Alexis (Industrie), Louis (Sales SaaS), Méroë Nguimbi (Sales général)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -660,346 +645,1094 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENTREPRISES UNIQUES</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hospitality</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>19</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>## 1. Volumes par vertical</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Industrie</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>20</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>| Vertical | Destinataire | Lignes | Entreprises uniques | Contacts sourcés | % sourcé |</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TOP ENTREPRISES FINANCE</t>
+          <t>|---|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Capeos Conseils</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>| Finance | Valentin | 38 / 40 | 18 | 5 | 13 % |</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Conserverie Chancerelle</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>| Hospitality | Valentin | 40 / 40 | 19 | 3 | 8 % |</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EUREX</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>| Industrie | Alexis | 40 / 40 | 20 | 3 | 8 % |</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Endrix</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>| Sales SaaS | Louis | 40 / 40 | 20 | **20** | **50 %** |</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fidaco</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>| Sales général | Méroë | 40 / 40 | 20 | 3 | 8 % |</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Groupe Archipel</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>| **TOTAL** | | **198** | **97** | **34** | **17 %** |</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Nextories</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PME - Credit Manager Saint-Alban 31 (NC)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>**Répartition JOB / NEWS**</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PME Bouches-du-Rhône (NC)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PME Gironde (NC)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>| Vertical | JOB | NEWS |</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TOP ENTREPRISES HOSPITALITY</t>
+          <t>| Finance | 29 | 9 |</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Château de Bagnols</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>| Hospitality | 28 | 12 |</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Highstay</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>| Industrie | 28 | 12 |</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hôtel Bowmann</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>| Sales SaaS | 28 | 12 |</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hôtel Chais Monnet</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>| Sales général | 40 | 0 |</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Hôtel D'Orsay</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="A38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hôtel Le Morgane</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Hôtel Le Pigonnet</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hôtel Miss Fuller</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>## 2. Top régions / villes / secteurs</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Hôtel Napoléon Paris</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hôtel Restaurant La Co(o)rniche</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>**Finance** — Paris (75) domine avec 11 lignes, puis Lyon (69) 4, Douarnenez (29) 3, et une</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>diagonale francilienne périphérique (Orly 94, Le Blanc-Mesnil 93, Taverny 95). Secteurs : cabinets</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TOP ENTREPRISES INDUSTRIE</t>
+          <t>d'expertise comptable indépendants en consolidation, ETI familiales industrielles, médico-social.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Bouyer Leroux</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Eolane</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>**Hospitality** — Paris (75) très majoritaire (18 lignes), Chamonix (74) 4, puis un chapelet</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gagne</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>d'établissements de province et d'outre-mer : Cognac (16), La Teste-de-Buch (33), Loir-et-Cher (41),</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Groupe Clim</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>Polynésie (987). Secteurs : hôtellerie 4-5* indépendante, ouvertures et pré-ouvertures.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>K-Line (Groupe Liebot)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lauak</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>**Industrie** — La verticale la plus régionale, conformément à la consigne géographique.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mecalac</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>Pays de la Loire en tête : Maine-et-Loire (49) 6 lignes, Vendée (85) 4. Puis Lot (46), Nord (59),</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Novatics</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>Haute-Loire (43), Finistère (29). Secteurs : sous-traitance aéronautique, matériaux de construction,</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Omerin</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>électronique industrielle, agroalimentaire.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Pack'R</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="A55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>**Sales SaaS** — Concentration parisienne assumée (75) 28 lignes, Lyon (69) 6, Hauts-de-Seine (92) 4,</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NOTE BEST-EFFORT</t>
+          <t>Yvelines (78) 2. Secteurs : SaaS vertical métier (santé au travail, expertise comptable, restauration),</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Budget WebSearch (200 req/agent) épuisé — sourçage nominatif limité.</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>deeptech, fintech B2B.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Finance A : 2 opportunités (Chancerelle Douarnenez) — proxy réseau bloquant.</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zwilling Staub (Industrie) + K-Line (Industrie) : effectif groupe à valider.</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>**Sales général** — La mieux répartie : Marne (51) 4, Bouches-du-Rhône (13) 4, Haute-Garonne (31) 4,</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>puis Rhône (69), Tarn (81), Finistère (29). Secteurs : négoce de matériaux, instrumentation de mesure,</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>services à la personne, distribution B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>## 3. Top 7 signaux business prioritaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1. **MyUnisoft** (Saint-Quentin-en-Yvelines, 253 sal.) — Plan de 100 recrutements sur 2026, soit un</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   passage de 253 à 353 collaborateurs, sous actionnariat majoritaire **HgCapital**. Le meilleur signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   du jour : volume, capital patient, éditeur peu médiatisé. → **LOUIS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2. **padoa** (Paris) — **Thoma Bravo** prend le majoritaire via son fonds Europe de 1,8 Md€ ;</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Five Arrows et Kamet réinvestissent. Plan d'expansion DACH annoncé, donc recrutements commerciaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   à venir. → **LOUIS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3. **Groupe Derrey** (Étival-Clairefontaine, 88, 600 sal.) — Campagne de 26 postes en CDI dans le</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Grand Est, dont plusieurs profils commerce ; annonce technico-commercial ouverte à Épinal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Négociant en matériaux indépendant, exactement notre cible. → **MÉROË**</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4. **N2JSoft / N2F** (Lyon, 70 → 130 sal. en un an, &gt; 10 M€ de CA) — Recrute simultanément</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sales Enablement Manager, RevOps Manager et SDR : refonte complète de la machine commerciale</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   d'un éditeur indépendant et discret. → **LOUIS**</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>5. **FDG Group** (Orly, 94, 630 sal., 117 M€ de CA) — Deux postes de contrôle de gestion ouverts en</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   parallèle (business partner opérationnel + corporate) : renforcement net et simultané de l'équipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   CDG, signal classique de structuration. → **VALENTIN**</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>6. **Chauvin Arnoux** (instrumentation de mesure, groupe familial indépendant, 430 sal., 57 M€) —</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Création d'un poste d'ingénieur technico-commercial itinérant sur la zone Toulouse : ouverture de</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   territoire, pas un remplacement. → **MÉROË**</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>7. **Techmo Hygiène** (Le Blanc-Mesnil, 93, 280 sal., groupe familial indépendant depuis 1947) —</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Comptable général expérimenté avec encadrement de deux comptables fournisseurs : structuration de</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   la fonction comptable dans une PME patrimoniale. → **VALENTIN**</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>## 4. Récurrences</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Périmètre scanné : **172 entreprises** déjà ciblées par les fichiers des 01/09, 02/09 et 03/09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ces entreprises sont exclues de la nouvelle recherche, mais vérifiées pour signal frais (27/08 → 03/09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>**3 récurrences confirmées :**</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>- **Figeac Aéro** (aéronautique / défense) — Chiffre d'affaires T1 2026/27 à 111,8 M€, 21e trimestre</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  consécutif de croissance (+11,6 % organique), carnet de commandes record à 5 Md€ — 02/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Signal de croissance soutenue, angle Industrie et Finance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>- **Voyageurs du Monde** (tourisme sur mesure) — AVANTAGE (86,59 % du capital) annonce une offre</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  publique de retrait à 180 € par action et la sortie de cote d'Euronext Paris — 01/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Sortie de cote : réorganisation probable des fonctions support, angle Finance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>- **STIF** (industrie, sécurité explosion et stockage d'énergie) — Déclaration mensuelle de droits de</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  vote au 31/08 — 02/09/2026. Signal réglementaire de routine, **faible valeur commerciale**.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Le détail, y compris les pistes écartées faute de datation dans la fenêtre, est dans</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>`outputs/_recurrences_2026-09-03.md`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>## 5. Filtres appliqués</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>**Liste noire** — appliquée aux cinq verticales : Big 4, next tier (Mazars, Grant Thornton, BDO, RSM,</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Baker Tilly), réseaux d'expertise comptable (In Extenso, Fiducial, Cerfrance, Exco, Sofarec),</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>scale-ups surmédiatisées, CAC 40, et cabinets d'intérim masquant le client final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>**Plafond 2000 salariés au niveau groupe** — exclusions prononcées aujourd'hui :</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Padam Mobility (filiale Siemens Mobility), Mabéo Industries (groupe Martin Belaysoud),</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Fnac Darty, Primagaz, Jacquet Brossard, Agicap (FT120, trop visible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Intermédiaires écartés pour employeur final masqué : Dream Catcher Sales, Tomcat Talents, Jobglober.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Écartés faute d'effectif vérifiable : Nopillo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>**Alternance / stage** — zéro annonce en alternance, apprentissage, contrat pro ou stage dans les</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>fichiers livrés. Wimi a été écarté à ce titre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>**Anti-doublons 14 jours** — les 172 entreprises déjà ciblées sont absentes des cinq fichiers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>## 6. Dédoublonnage Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Le fichier de Méroë a été confronté au fichier de Louis sur la colonne `entreprise` :</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>**aucune entreprise retirée**, les deux agents ayant travaillé sur des périmètres disjoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>(l'agent Sales général avait pour consigne d'éviter les éditeurs SaaS et tech B2B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Les deux fichiers sortent donc à 40 lignes pleines, 20 entreprises chacun, sans recouvrement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>## 7. Limites du run — à lire</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Ce run mérite trois réserves explicites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>**Contacts non sourcés.** Sur 198 lignes, 34 seulement portent un nom. Le budget de recherche web de</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>la session (200 requêtes, partagé entre tous les agents) a été épuisé avant la phase de sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>nominatif sur quatre verticales sur cinq. Seul le fichier Sales SaaS de Louis atteint 50 % de contacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>nommés. **Aucun nom n'a été inventé** : les lignes non sourcées portent le tag `CONTACT_NON_SOURCE`</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>et des colonnes `nom` / `prenom` / `linkedin` vides, à enrichir via FullEnrich ou une session dédiée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>**Dates de publication majoritairement en `NC`.** Le proxy de cet environnement bloque en accès direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>la quasi-totalité des sources utiles — APEC, Indeed, Hellowork, LinkedIn, Welcome to the Jungle,</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>France Travail, Pappers, Societe.com, ainsi que la plupart des sites carrière. Le travail s'est fait</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>sur les extraits de résultats de recherche. Les annonces retenues sont des offres réellement en ligne</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>au 03/09/2026 à employeur nommé, mais la fenêtre « publiée dans les 7 derniers jours » n'est pas</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>confirmable pour la majorité d'entre elles. Chaque ligne porte sa date réelle ou `NC` dans les notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>**Deux écarts de volume assumés.** Finance sort à 38 lignes au lieu de 40 (la partie A, comptabilité</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>générale et contrôle de gestion, n'a pas trouvé une cinquième opportunité vérifiable). Sales général</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>sort à 40 lignes mais avec 40 JOB et 0 NEWS : toutes les pistes NEWS remontées ont été écartées après</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>vérification — dates réelles hors fenêtre (Partedis, FATEC Group, Aditec) ou effectif groupe au-dessus</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>du plafond. Aucun signal n'a été fabriqué pour combler le quota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>## 8. Fichiers livrés</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>| Fichier | Lignes | Destinataire |</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>| `outputs/finance_2026-09-03.csv` | 38 | Valentin Murcia |</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>| `outputs/hospitality_2026-09-03.csv` | 40 | Valentin Murcia |</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>| `outputs/industrie_2026-09-03.csv` | 40 | Alexis |</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>| `outputs/sales_saas_2026-09-03.csv` | 40 | Louis |</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>| `outputs/sales_2026-09-03.csv` | 40 | Méroë Nguimbi |</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>| `outputs/humanup_market_mapping_2026-09-03.xlsx` | 6 onglets | Méroë Nguimbi |</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>| `outputs/rapport_synthese_2026-09-03.md` | — | Méroë Nguimbi |</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Fichiers intermédiaires conservés pour traçabilité : `_fin_a`, `_fin_a_complement`, `_fin_b`,</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>`_fin_c`, `_sales_complement`, `_recurrences`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>## 9. Actions prioritaires</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1. **Attaquer MyUnisoft et padoa aujourd'hui** (Louis). Ce sont les deux signaux les plus chauds du</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   jour et les seuls adossés à un fonds avec un plan de recrutement explicite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2. **Lancer l'enrichissement FullEnrich** sur les 164 lignes `CONTACT_NON_SOURCE` avant toute</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   séquence d'approche : les fichiers Finance, Hospitality, Industrie et Sales général sont</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   inexploitables en l'état sans noms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>3. **Groupe Derrey** (Méroë) : 26 postes ouverts d'un coup chez un négociant indépendant de 600</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   salariés, c'est un mandat multi-postes potentiel, pas une mission unitaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>4. **Requalifier les dates** des annonces marquées `NC` avant approche, depuis un poste ayant accès</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   à l'APEC et à LinkedIn : une annonce de plus de trois semaines change l'angle d'appel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>5. **Prévoir une session de sourcing dédiée** avec budget de recherche réservé, pour ne pas</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   reproduire l'épuisement constaté sur ce run.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1012,16 +1745,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="51" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -1029,57 +1762,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>prenom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>poste</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>entreprise</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>localisation</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>linkedin</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1111,7 +1844,7 @@
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>FINANCE,JOB,N+1,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1148,7 +1881,7 @@
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>FINANCE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -1185,7 +1918,7 @@
           <t>France Travail / Hellowork</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>FINANCE,JOB,N+1,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -1203,33 +1936,33 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DRH</t>
+          <t>Responsable comptable / Chef comptable</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Conserverie Chancerelle</t>
+          <t>APAJH du Val d'Oise</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Douarnenez (29)</t>
+          <t>Taverny (95)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>France Travail / Hellowork</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
+          <t>Taleez</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,CHEF_COMPTABLE,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Poste: Contrôleur de Gestion Industriel H/F | Date: NC | Effectif: 1900 | CA: 182M€ | Salaire: NC | Source: France Travail (ref 207WYYQ) | Lien: https://www.hellowork.com/fr-fr/emplois/74613421.html | Contexte: Idem contact 1. DRH non identifié. Profil Bac+3 à Bac+5 contrôle de gestion/management industriel requis.</t>
+          <t>Poste: Comptable H/F (comptabilite generale - siege) | Date: 2026-09-01 | Effectif: 825 professionnels (23 etablissements) | CA: NC | Salaire: NC | Source: Taleez (page carriere APAJH 95) | Lien: https://taleez.com/apply/comptable-h-f-taverny-apajh-du-val-d-oise-cdi | Contexte: Association gestionnaire independante du handicap dans le 95 - 23 etablissements et services - siege de 39 personnes a Taverny. Offre comptable publiee le 01/09/2026 (recoupee LinkedIn Jobs 'il y a 3 jours'). Structure multi-etablissements avec comptabilite centralisee au siege.</t>
         </is>
       </c>
     </row>
@@ -1240,33 +1973,33 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Expert-comptable associé</t>
+          <t>DRH</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stengelin</t>
+          <t>APAJH du Val d'Oise</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Taverny (95)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>welcometothejungle.com</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,EC_ASSOCIE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+          <t>Taleez</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Poste: Directeur de Mission Expertise Comptable | Date: 2026-08-27 | Effectif: ~50 | CA: NC | Salaire: NC | Source: welcometothejungle.com | Lien: https://www.welcometothejungle.com/fr/companies/stengelin/jobs/directeur-de-mission-expertise-comptable-cdi-h-f | Contexte: Cabinet parisien indépendant ~50 salariés certifié Great Place to Work. Recrute Directeur de Mission EC en CDI pour accompagner PME/ETI sur missions comptables à forte valeur ajoutée.</t>
+          <t>Poste: Comptable H/F (comptabilite generale - siege) | Date: 2026-09-01 | Effectif: 825 professionnels (23 etablissements) | CA: NC | Salaire: NC | Source: Taleez (page carriere APAJH 95) | Lien: https://taleez.com/apply/comptable-h-f-taverny-apajh-du-val-d-oise-cdi | Contexte: Association gestionnaire independante du handicap dans le 95 - 23 etablissements et services - siege de 39 personnes a Taverny. Offre comptable publiee le 01/09/2026 (recoupee LinkedIn Jobs 'il y a 3 jours'). Structure multi-etablissements avec comptabilite centralisee au siege.</t>
         </is>
       </c>
     </row>
@@ -1277,29 +2010,33 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DRH</t>
+          <t>Associe / Directeur de bureau Expertise Comptable</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stengelin</t>
+          <t>ADVOLIS ORFIS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Villeurbanne (69)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Taleez</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,HIRING_MANAGER,NC,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Poste: Directeur de Mission Expertise Comptable | Date: 2026-08-27 | Effectif: ~50 | CA: NC | Salaire: NC | Source: welcometothejungle.com | Lien: https://www.welcometothejungle.com/fr/companies/stengelin/jobs/directeur-de-mission-expertise-comptable-cdi-h-f | Contexte: Cabinet parisien indépendant ~50 salariés certifié Great Place to Work. Recrute Directeur de Mission EC en CDI pour accompagner PME/ETI sur missions comptables à forte valeur ajoutée.</t>
+          <t>Poste: Collaborateur Comptable Senior H/F | Date: 2026-09-01 | Effectif: NC (cabinet independant multi-bureaux) | CA: NC | Salaire: NC | Source: Taleez (page carriere Advolis Orfis) | Lien: https://taleez.com/apply/collaborateur-comptable-senior-h-f-villeurbanne-advolis-orfis-cdi | Contexte: Cabinet d'audit et d'expertise comptable independant (hors Big 4 et hors reseaux nationaux), bureau de Villeurbanne. Offre publiee le 01/09/2026 - poste de comptable senior confirme. Recoupement LinkedIn Jobs : poste comptable general CDI Villeurbanne publie il y a 2 jours.</t>
         </is>
       </c>
     </row>
@@ -1310,33 +2047,33 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Associé gérant</t>
+          <t>DRH</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Capeos Conseils</t>
+          <t>ADVOLIS ORFIS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Redon (35)</t>
+          <t>Villeurbanne (69)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>redon-emplois.com</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,ASSOC_GERANT,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+          <t>Taleez</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,NC,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Poste: Chef de Mission Comptable | Date: 2026-07-03 | Effectif: 420 | CA: NC | Salaire: NC | Source: redon-emplois.com | Lien: https://www.redon-emplois.com/emplois/80945490.html | Contexte: Cabinet régional breton indépendant 420 salariés sur 17 sites (Ille-et-Vilaine, Côtes-d'Armor, Pays de la Loire, 10 000 clients). Recrute Chef de Mission en CDI à Redon pour consolider son ancrage local.</t>
+          <t>Poste: Collaborateur Comptable Senior H/F | Date: 2026-09-01 | Effectif: NC (cabinet independant multi-bureaux) | CA: NC | Salaire: NC | Source: Taleez (page carriere Advolis Orfis) | Lien: https://taleez.com/apply/collaborateur-comptable-senior-h-f-villeurbanne-advolis-orfis-cdi | Contexte: Cabinet d'audit et d'expertise comptable independant (hors Big 4 et hors reseaux nationaux), bureau de Villeurbanne. Offre publiee le 01/09/2026 - poste de comptable senior confirme. Recoupement LinkedIn Jobs : poste comptable general CDI Villeurbanne publie il y a 2 jours.</t>
         </is>
       </c>
     </row>
@@ -1347,70 +2084,70 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DRH</t>
+          <t>DAF / Directeur Administratif et Financier</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Capeos Conseils</t>
+          <t>Techmo Hygiene</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Redon (35)</t>
+          <t>Le Blanc-Mesnil (93)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Taleez</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Poste: Chef de Mission Comptable | Date: 2026-07-03 | Effectif: 420 | CA: NC | Salaire: NC | Source: redon-emplois.com | Lien: https://www.redon-emplois.com/emplois/80945490.html | Contexte: Cabinet régional breton indépendant 420 salariés sur 17 sites (Ille-et-Vilaine, Côtes-d'Armor, Pays de la Loire, 10 000 clients). Recrute Chef de Mission en CDI à Redon pour consolider son ancrage local.</t>
+          <t>Poste: Comptable General H/F (encadre 2 comptables fournisseurs) | Date: NC (offre active au 03/09/2026 - date de publication non verifiable, job boards bloques par le proxy) | Effectif: 280 salaries repartis sur 4 societes | CA: NC | Salaire: NC | Source: Taleez (page carriere Techmo Hygiene) - recoupee Jobintree ref 81388913 | Lien: https://taleez.com/apply/comptable-general-h-f-le-blanc-mesnil-techmo-hygiene-cdi | Contexte: Groupe familial independant fonde en 1947 (lutte antiparasitaire - 4 societes - 280 salaries) - siege ZI du Coudray au Blanc-Mesnil. Recherche un comptable general 7 ans d'experience PME sur SAGE 1000 avec encadrement temporaire de 2 comptables fournisseurs : signal de structuration de la fonction comptable.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Maxime</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Co-fondateur &amp; Directeur Général</t>
+          <t>DRH</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Groupe Archipel</t>
+          <t>Techmo Hygiene</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Le Blanc-Mesnil (93)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>groupearchipel.com</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,ASSOC_GERANT,50-500,CONTACT_1</t>
+          <t>Taleez</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Poste: Collaborateur Comptable Confirmé (Lamy Experts) | Date: 2026-06-15 | Effectif: 450 | CA: 60M€ | Salaire: NC | Source: lamacompta.co | Lien: https://lamacompta.co/cabinets/archipel/offres/collaborateur-comptable-confirme-lamy-experts-f-h-22950 | Contexte: Groupe Archipel (10 cabinets, 450 collaborateurs) recrute chez Lamy Experts à Paris. Groupe PE-backed (Alpera/Eurazeo) en forte expansion nationale, clientèle PME/TPE/professions libérales.</t>
+          <t>Poste: Comptable General H/F (encadre 2 comptables fournisseurs) | Date: NC (offre active au 03/09/2026 - date de publication non verifiable, job boards bloques par le proxy) | Effectif: 280 salaries repartis sur 4 societes | CA: NC | Salaire: NC | Source: Taleez (page carriere Techmo Hygiene) - recoupee Jobintree ref 81388913 | Lien: https://taleez.com/apply/comptable-general-h-f-le-blanc-mesnil-techmo-hygiene-cdi | Contexte: Groupe familial independant fonde en 1947 (lutte antiparasitaire - 4 societes - 280 salaries) - siege ZI du Coudray au Blanc-Mesnil. Recherche un comptable general 7 ans d'experience PME sur SAGE 1000 avec encadrement temporaire de 2 comptables fournisseurs : signal de structuration de la fonction comptable.</t>
         </is>
       </c>
     </row>
@@ -1421,74 +2158,70 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DRH Groupe</t>
+          <t>Responsable Controle de Gestion (N+1 direct)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Groupe Archipel</t>
+          <t>FDG Group</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Orly (94)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Taleez</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,RESP_CONTROLE_GESTION,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Poste: Collaborateur Comptable Confirmé (Lamy Experts) | Date: 2026-06-15 | Effectif: 450 | CA: 60M€ | Salaire: NC | Source: lamacompta.co | Lien: https://lamacompta.co/cabinets/archipel/offres/collaborateur-comptable-confirme-lamy-experts-f-h-22950 | Contexte: Groupe Archipel (10 cabinets, 450 collaborateurs) recrute chez Lamy Experts à Paris. Groupe PE-backed (Alpera/Eurazeo) en forte expansion nationale, clientèle PME/TPE/professions libérales.</t>
+          <t>Poste: Controleur de Gestion Operationnel H/F (+ Controleur de Gestion Corporate H/F ouvert en parallele) | Date: NC (offre active au 03/09/2026 - date de publication non verifiable, job boards bloques par le proxy) | Effectif: 630 salaries (2023) | CA: 117 M EUR (2023) | Salaire: NC | Source: Taleez (page carriere FDG Group) - recoupee Hellowork ref 72362063 et 70886474 | Lien: https://taleez.com/apply/controleur-de-gestion-operationnel-h-f-orly-fdg-group-cdi | Contexte: Groupe francais independant de creation et distribution de produits non alimentaires en GMS (textile - bazar - hygiene-beaute) base a Orly. Deux postes de controle de gestion ouverts simultanement (operationnel en business partner gammes + corporate) : signal net de renforcement de l'equipe controle de gestion.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Louis</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chef de Mission</t>
+          <t>DRH / Talent Acquisition</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EUREX</t>
+          <t>FDG Group</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gennevilliers (92)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/louis-camus-74940cr21/</t>
-        </is>
-      </c>
+          <t>Orly (94)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>linkedin.com</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DIR_AUDIT,500-2000,CONTACT_1</t>
+          <t>Taleez</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,TALENT_ACQUISITION,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Poste: Chef de Mission Comptable | Date: 2026-08-27 | Effectif: 850 | CA: NC | Salaire: NC | Source: linkedin.com | Lien: https://fr.linkedin.com/company/eurex_2 | Contexte: EUREX groupe 850 collaborateurs, 60+ agences en France, recrute Chef de Mission à Gennevilliers (92). Cabinet fondé en 1962, réseau national présent depuis plus de 60 ans, expertise comptable, audit et conseil.</t>
+          <t>Poste: Controleur de Gestion Operationnel H/F (+ Controleur de Gestion Corporate H/F ouvert en parallele) | Date: NC (offre active au 03/09/2026 - date de publication non verifiable, job boards bloques par le proxy) | Effectif: 630 salaries (2023) | CA: 117 M EUR (2023) | Salaire: NC | Source: Taleez (page carriere FDG Group) - recoupee Hellowork ref 72362063 et 70886474 | Lien: https://taleez.com/apply/controleur-de-gestion-operationnel-h-f-orly-fdg-group-cdi | Contexte: Groupe francais independant de creation et distribution de produits non alimentaires en GMS (textile - bazar - hygiene-beaute) base a Orly. Deux postes de controle de gestion ouverts simultanement (operationnel en business partner gammes + corporate) : signal net de renforcement de l'equipe controle de gestion.</t>
         </is>
       </c>
     </row>
@@ -1499,29 +2232,33 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DRH / Talent Acquisition</t>
+          <t>President / Directeur General</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EUREX</t>
+          <t>Medimex</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gennevilliers (92)</t>
+          <t>Sainte-Foy-les-Lyon (69)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CFNEWS</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,NEWS,DG,NC,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Poste: Chef de Mission Comptable | Date: 2026-08-27 | Effectif: 850 | CA: NC | Salaire: NC | Source: linkedin.com | Lien: https://fr.linkedin.com/company/eurex_2 | Contexte: EUREX groupe 850 collaborateurs, 60+ agences en France, recrute Chef de Mission à Gennevilliers (92). Cabinet fondé en 1962, réseau national présent depuis plus de 60 ans, expertise comptable, audit et conseil.</t>
+          <t>Poste: Signal NEWS - OBO/LBO avec un fonds a impact | Date: NC (article CFNEWS 2026 - date exacte non verifiable, contenu sous paywall) | Effectif: NC | CA: ~30 M EUR (2025) | Salaire: NC | Source: CFNEWS (rubrique LBO/OBO) | Lien: https://www.cfnews.net/L-actualite/LBO/Operations/OBO/Medimex-s-eduque-au-LBO-avec-un-fonds-impact-554347 | Fonds: fonds a impact (nom non communique dans la partie publique de l'article) | Montant: NC | Contexte: PME lyonnaise (Sainte-Foy-les-Lyon) de distribution - maintenance et reconditionnement de dispositifs medicaux et materiel de reeducation - CA ~30 M EUR double en 3-4 ans avec une marge d'EBITDA ~15 pourcent. Entree d'un fonds a impact au capital : reporting investisseur - controle de gestion et structuration comptable a construire.</t>
         </is>
       </c>
     </row>
@@ -1532,33 +2269,33 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Expert-comptable associé</t>
+          <t>DRH</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fidaco</t>
+          <t>Medimex</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Angers (49)</t>
+          <t>Sainte-Foy-les-Lyon (69)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>fidaco.com</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,EC_ASSOCIE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+          <t>CFNEWS</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,NEWS,DRH,NC,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Poste: Chef de Mission Audit | Date: 2026-08-27 | Effectif: NC | CA: NC | Salaire: NC | Source: fidaco.com | Lien: https://fidaco.com/chef-de-mission-audit-h-f/ | Contexte: Cabinet d'expertise comptable angevin indépendant recrute Chef de Mission Audit en CDI via son propre site. Effectif non vérifié (accès bloqué) – cabinet estimé à taille humaine &lt; 100 sal.</t>
+          <t>Poste: Signal NEWS - OBO/LBO avec un fonds a impact | Date: NC (article CFNEWS 2026 - date exacte non verifiable, contenu sous paywall) | Effectif: NC | CA: ~30 M EUR (2025) | Salaire: NC | Source: CFNEWS (rubrique LBO/OBO) | Lien: https://www.cfnews.net/L-actualite/LBO/Operations/OBO/Medimex-s-eduque-au-LBO-avec-un-fonds-impact-554347 | Fonds: fonds a impact (nom non communique dans la partie publique de l'article) | Montant: NC | Contexte: PME lyonnaise (Sainte-Foy-les-Lyon) de distribution - maintenance et reconditionnement de dispositifs medicaux et materiel de reeducation - CA ~30 M EUR double en 3-4 ans avec une marge d'EBITDA ~15 pourcent. Entree d'un fonds a impact au capital : reporting investisseur - controle de gestion et structuration comptable a construire.</t>
         </is>
       </c>
     </row>
@@ -1569,49 +2306,49 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DRH</t>
+          <t>Expert-comptable associé</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fidaco</t>
+          <t>Stengelin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Angers (49)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>welcometothejungle.com</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,EC_ASSOCIE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Poste: Chef de Mission Audit | Date: 2026-08-27 | Effectif: NC | CA: NC | Salaire: NC | Source: fidaco.com | Lien: https://fidaco.com/chef-de-mission-audit-h-f/ | Contexte: Cabinet d'expertise comptable angevin indépendant recrute Chef de Mission Audit en CDI via son propre site. Effectif non vérifié (accès bloqué) – cabinet estimé à taille humaine &lt; 100 sal.</t>
+          <t>Poste: Directeur de Mission Expertise Comptable | Date: 2026-08-27 | Effectif: ~50 | CA: NC | Salaire: NC | Source: welcometothejungle.com | Lien: https://www.welcometothejungle.com/fr/companies/stengelin/jobs/directeur-de-mission-expertise-comptable-cdi-h-f | Contexte: Cabinet parisien indépendant ~50 salariés certifié Great Place to Work. Recrute Directeur de Mission EC en CDI pour accompagner PME/ETI sur missions comptables à forte valeur ajoutée.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Clément</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Associé - Commissariat aux Comptes</t>
+          <t>DRH</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Endrix</t>
+          <t>Stengelin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1620,112 +2357,104 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>compta-online.com</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>FINANCE,NEWS,DIR_AUDIT,500-2000,CONTACT_1</t>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Poste: Associé Audit/CAC (signal: nomination 5 nouveaux associés 2026) | Date: 2026-08-15 | Effectif: 850 | CA: 60M€ | Salaire: NC | Source: compta-online.com | Lien: https://www.compta-online.com/endrix-ao8343 | Contexte: Endrix nomme 5 nouveaux associés (dont Clément Chatelus, audit) et intègre 5 cabinets en 2026. Fort signal de recrutement : 35 sites, objectif 300M€ CA à 2030, structuration DRH active.</t>
+          <t>Poste: Directeur de Mission Expertise Comptable | Date: 2026-08-27 | Effectif: ~50 | CA: NC | Salaire: NC | Source: welcometothejungle.com | Lien: https://www.welcometothejungle.com/fr/companies/stengelin/jobs/directeur-de-mission-expertise-comptable-cdi-h-f | Contexte: Cabinet parisien indépendant ~50 salariés certifié Great Place to Work. Recrute Directeur de Mission EC en CDI pour accompagner PME/ETI sur missions comptables à forte valeur ajoutée.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Nicolas</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Responsable Conseil en Recrutement</t>
+          <t>Associé gérant</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Endrix</t>
+          <t>Capeos Conseils</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Redon (35)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>endrix.com</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>FINANCE,NEWS,DRH,500-2000,CONTACT_2</t>
+          <t>redon-emplois.com</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,ASSOC_GERANT,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Poste: Responsable Recrutement (signal: nomination 5 associés + expansion 2026) | Date: 2026-08-15 | Effectif: 850 | CA: 60M€ | Salaire: NC | Source: endrix.com | Lien: https://www.endrix.com/blog/groupe/endrix-conseil-recrutement/ | Contexte: Nicolas Tertrais (ex-Hodas RH) rejoint Endrix pour structurer le pôle recrutement. Signal de montée en puissance RH en vue de recrutements massifs liés à la croissance organique et externe.</t>
+          <t>Poste: Chef de Mission Comptable | Date: 2026-07-03 | Effectif: 420 | CA: NC | Salaire: NC | Source: redon-emplois.com | Lien: https://www.redon-emplois.com/emplois/80945490.html | Contexte: Cabinet régional breton indépendant 420 salariés sur 17 sites (Ille-et-Vilaine, Côtes-d'Armor, Pays de la Loire, 10 000 clients). Recrute Chef de Mission en CDI à Redon pour consolider son ancrage local.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Matthieu</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Co-fondateur</t>
+          <t>DRH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Groupe Archipel</t>
+          <t>Capeos Conseils</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Redon (35)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>compta-online.com</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>FINANCE,NEWS,ASSOC_GERANT,50-500,CONTACT_1</t>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Poste: Co-fondateur Archipel (signal: levée 65M€ + 5 acquisitions H1 2026) | Date: 2026-04-15 | Effectif: 450 | CA: 60M€ | Salaire: NC | Source: compta-online.com | Lien: https://www.compta-online.com/groupe-archipel-ao7777 | Contexte: Archipel lève 65M€ (Eurazeo) et acquiert Prospective &amp; Finance (48 sal, Soissons), Avexxens (33 sal, Antony) et L&amp;A Conseil &amp; Audit (Paris) en avril 2026. Besoins de recrutement structurels liés à l'intégration et à la cible de 150M€ CA en 2029.</t>
+          <t>Poste: Chef de Mission Comptable | Date: 2026-07-03 | Effectif: 420 | CA: NC | Salaire: NC | Source: redon-emplois.com | Lien: https://www.redon-emplois.com/emplois/80945490.html | Contexte: Cabinet régional breton indépendant 420 salariés sur 17 sites (Ille-et-Vilaine, Côtes-d'Armor, Pays de la Loire, 10 000 clients). Recrute Chef de Mission en CDI à Redon pour consolider son ancrage local.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ridel</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Maxime</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DRH Groupe</t>
+          <t>Co-fondateur &amp; Directeur Général</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1739,15 +2468,19 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>groupearchipel.com</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,ASSOC_GERANT,50-500,CONTACT_1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Poste: DRH (signal: levée 65M€ + 5 acquisitions H1 2026) | Date: 2026-04-15 | Effectif: 450 | CA: 60M€ | Salaire: NC | Source: compta-online.com | Lien: https://www.compta-online.com/groupe-archipel-ao7777 | Contexte: Archipel lève 65M€ (Eurazeo) et acquiert Prospective &amp; Finance (48 sal, Soissons), Avexxens (33 sal, Antony) et L&amp;A Conseil &amp; Audit (Paris) en avril 2026. Besoins de recrutement structurels liés à l'intégration et à la cible de 150M€ CA en 2029.</t>
+          <t>Poste: Collaborateur Comptable Confirmé (Lamy Experts) | Date: 2026-06-15 | Effectif: 450 | CA: 60M€ | Salaire: NC | Source: lamacompta.co | Lien: https://lamacompta.co/cabinets/archipel/offres/collaborateur-comptable-confirme-lamy-experts-f-h-22950 | Contexte: Groupe Archipel (10 cabinets, 450 collaborateurs) recrute chez Lamy Experts à Paris. Groupe PE-backed (Alpera/Eurazeo) en forte expansion nationale, clientèle PME/TPE/professions libérales.</t>
         </is>
       </c>
     </row>
@@ -1758,12 +2491,12 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Directeur Financier</t>
+          <t>DRH Groupe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Voyageurs du Monde</t>
+          <t>Groupe Archipel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1772,56 +2505,64 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>LinkedIn Jobs / Indeed</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Poste: Gestionnaire de paie | Date: 2026-08-28 | Effectif: ~350 | CA: NC | Salaire: 30-36K€ | Source: LinkedIn Jobs | Lien: https://fr.linkedin.com/jobs/view/gestionnaire-de-paie-at-voyageurs-du-monde-2963369195 | Contexte: Leader français du voyage sur mesure fondé 1979, ~350 sal dont ~100 en régions. Recrute gestionnaire de paie CDI en équipe de 4 (paie+ADP), Paris 75, vu actif sur Indeed le 02/09/2026. Logiciel Sage, télétravail 2j/sem, participation, TR.</t>
+          <t>Poste: Collaborateur Comptable Confirmé (Lamy Experts) | Date: 2026-06-15 | Effectif: 450 | CA: 60M€ | Salaire: NC | Source: lamacompta.co | Lien: https://lamacompta.co/cabinets/archipel/offres/collaborateur-comptable-confirme-lamy-experts-f-h-22950 | Contexte: Groupe Archipel (10 cabinets, 450 collaborateurs) recrute chez Lamy Experts à Paris. Groupe PE-backed (Alpera/Eurazeo) en forte expansion nationale, clientèle PME/TPE/professions libérales.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Camus</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Louis</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DRH</t>
+          <t>Chef de Mission</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Voyageurs du Monde</t>
+          <t>EUREX</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Gennevilliers (92)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louis-camus-74940cr21/</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LinkedIn Jobs / Indeed</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+          <t>linkedin.com</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DIR_AUDIT,500-2000,CONTACT_1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Poste: Gestionnaire de paie | Date: 2026-08-28 | Effectif: ~350 | CA: NC | Salaire: 30-36K€ | Source: LinkedIn Jobs | Lien: https://fr.linkedin.com/jobs/view/gestionnaire-de-paie-at-voyageurs-du-monde-2963369195 | Contexte: Idem contact 1. DRH non identifié (site voyageursdumonde.fr bloqué proxy). Groupe privé 350 sal, Paris 75.</t>
+          <t>Poste: Chef de Mission Comptable | Date: 2026-08-27 | Effectif: 850 | CA: NC | Salaire: NC | Source: linkedin.com | Lien: https://fr.linkedin.com/company/eurex_2 | Contexte: EUREX groupe 850 collaborateurs, 60+ agences en France, recrute Chef de Mission à Gennevilliers (92). Cabinet fondé en 1962, réseau national présent depuis plus de 60 ans, expertise comptable, audit et conseil.</t>
         </is>
       </c>
     </row>
@@ -1832,33 +2573,29 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CEO / Fondateur</t>
+          <t>DRH / Talent Acquisition</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nextories</t>
+          <t>EUREX</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Gennevilliers (92)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Welcome to the Jungle</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Poste: RAF (Responsable Administratif et Financier) | Date: NC | Effectif: NC (&lt;50 est.) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/nextories/jobs/responsable-administratif-et-financier-raf-h-f_paris | Contexte: Nextories, première plateforme professionnelle de déménagement B2B, recrute son RAF CDI Paris. Reporting direct CEO, structuration compta/tréso/social/fiscal. CEO/Fondateur non identifié (LinkedIn + WTJJ bloqués proxy).</t>
+          <t>Poste: Chef de Mission Comptable | Date: 2026-08-27 | Effectif: 850 | CA: NC | Salaire: NC | Source: linkedin.com | Lien: https://fr.linkedin.com/company/eurex_2 | Contexte: EUREX groupe 850 collaborateurs, 60+ agences en France, recrute Chef de Mission à Gennevilliers (92). Cabinet fondé en 1962, réseau national présent depuis plus de 60 ans, expertise comptable, audit et conseil.</t>
         </is>
       </c>
     </row>
@@ -1869,33 +2606,33 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DRH / Office Manager</t>
+          <t>Expert-comptable associé</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nextories</t>
+          <t>Fidaco</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Angers (49)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+          <t>fidaco.com</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,EC_ASSOCIE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Poste: RAF (Responsable Administratif et Financier) | Date: NC | Effectif: NC (&lt;50 est.) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/nextories/jobs/responsable-administratif-et-financier-raf-h-f_paris | Contexte: Idem contact 1. Structure probablement &lt;50 sal, interlocuteur RH = CEO ou Office Manager. DRH formalisé peu probable à ce stade.</t>
+          <t>Poste: Chef de Mission Audit | Date: 2026-08-27 | Effectif: NC | CA: NC | Salaire: NC | Source: fidaco.com | Lien: https://fidaco.com/chef-de-mission-audit-h-f/ | Contexte: Cabinet d'expertise comptable angevin indépendant recrute Chef de Mission Audit en CDI via son propre site. Effectif non vérifié (accès bloqué) – cabinet estimé à taille humaine &lt; 100 sal.</t>
         </is>
       </c>
     </row>
@@ -1906,144 +2643,164 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>DAF / Directeur Financier</t>
+          <t>DRH</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Société industrielle - Somme (NC)</t>
+          <t>Fidaco</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ailly-sur-Noye (80)</t>
+          <t>Angers (49)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Hellowork (via Manpower)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Poste: RAF (Responsable Administratif et Financier) | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (Manpower) | Lien: https://www.hellowork.com/fr-fr/emplois/50860822.html | Contexte: Site industriel en croissance dans la Somme (80) recrute un RAF CDI via Manpower. Entreprise cliente non identifiée (Hellowork bloqué proxy). Signal visible août 2026. Contacter Manpower Amiens pour qualifier le client final.</t>
+          <t>Poste: Chef de Mission Audit | Date: 2026-08-27 | Effectif: NC | CA: NC | Salaire: NC | Source: fidaco.com | Lien: https://fidaco.com/chef-de-mission-audit-h-f/ | Contexte: Cabinet d'expertise comptable angevin indépendant recrute Chef de Mission Audit en CDI via son propre site. Effectif non vérifié (accès bloqué) – cabinet estimé à taille humaine &lt; 100 sal.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chatelus</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Clément</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>DRH</t>
+          <t>Associé - Commissariat aux Comptes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Société industrielle - Somme (NC)</t>
+          <t>Endrix</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ailly-sur-Noye (80)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Hellowork (via Manpower)</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+          <t>compta-online.com</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>FINANCE,NEWS,DIR_AUDIT,500-2000,CONTACT_1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Poste: RAF (Responsable Administratif et Financier) | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (Manpower) | Lien: https://www.hellowork.com/fr-fr/emplois/50860822.html | Contexte: Idem contact 1. Industrial Somme (80). A prioriser dès identification du client Manpower.</t>
+          <t>Poste: Associé Audit/CAC (signal: nomination 5 nouveaux associés 2026) | Date: 2026-08-15 | Effectif: 850 | CA: 60M€ | Salaire: NC | Source: compta-online.com | Lien: https://www.compta-online.com/endrix-ao8343 | Contexte: Endrix nomme 5 nouveaux associés (dont Clément Chatelus, audit) et intègre 5 cabinets en 2026. Fort signal de recrutement : 35 sites, objectif 300M€ CA à 2030, structuration DRH active.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tertrais</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DAF / Directeur Financier</t>
+          <t>Responsable Conseil en Recrutement</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PME - Credit Manager Saint-Alban 31 (NC)</t>
+          <t>Endrix</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Saint-Alban (31)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Indeed France</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+          <t>endrix.com</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>FINANCE,NEWS,DRH,500-2000,CONTACT_2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Poste: Credit Manager | Date: 2026-06 | Effectif: NC | CA: NC | Salaire: NC | Source: Indeed France | Lien: https://fr.indeed.com/q-credit-manager-emplois.html | Contexte: CDI Credit Manager basé au siège à Saint-Alban (31, Toulouse métropole). Missions: sécurisation risque clients, partenariat équipe commerciale, analyse financière, limites crédit, assurance-crédit, optimisation recouvrement. Entreprise non identifiée (Indeed bloqué proxy). Posting vu en juin 2026 sur Indeed.</t>
+          <t>Poste: Responsable Recrutement (signal: nomination 5 associés + expansion 2026) | Date: 2026-08-15 | Effectif: 850 | CA: 60M€ | Salaire: NC | Source: endrix.com | Lien: https://www.endrix.com/blog/groupe/endrix-conseil-recrutement/ | Contexte: Nicolas Tertrais (ex-Hodas RH) rejoint Endrix pour structurer le pôle recrutement. Signal de montée en puissance RH en vue de recrutements massifs liés à la croissance organique et externe.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Luneau</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Matthieu</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DRH</t>
+          <t>Co-fondateur</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PME - Credit Manager Saint-Alban 31 (NC)</t>
+          <t>Groupe Archipel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Saint-Alban (31)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Indeed France</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+          <t>compta-online.com</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>FINANCE,NEWS,ASSOC_GERANT,50-500,CONTACT_1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Poste: Credit Manager | Date: 2026-06 | Effectif: NC | CA: NC | Salaire: NC | Source: Indeed France | Lien: https://fr.indeed.com/q-credit-manager-emplois.html | Contexte: Idem contact 1. PME siège Saint-Alban (31). À qualifier en accédant Indeed ou en cherchant site:linkedin.com credit manager saint-alban 31.</t>
+          <t>Poste: Co-fondateur Archipel (signal: levée 65M€ + 5 acquisitions H1 2026) | Date: 2026-04-15 | Effectif: 450 | CA: 60M€ | Salaire: NC | Source: compta-online.com | Lien: https://www.compta-online.com/groupe-archipel-ao7777 | Contexte: Archipel lève 65M€ (Eurazeo) et acquiert Prospective &amp; Finance (48 sal, Soissons), Avexxens (33 sal, Antony) et L&amp;A Conseil &amp; Audit (Paris) en avril 2026. Besoins de recrutement structurels liés à l'intégration et à la cible de 150M€ CA en 2029.</t>
         </is>
       </c>
     </row>
@@ -2054,33 +2811,33 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DAF / Trésorier</t>
+          <t>Directeur Financier</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PME Bouches-du-Rhône (NC)</t>
+          <t>Voyageurs du Monde</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuveau (13)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Hellowork</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,NEWS,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+          <t>LinkedIn Jobs / Indeed</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Poste: Trésorier | Date: 2026-09-02 | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (màj 02/09/2026) | Lien: https://www.hellowork.com/fr-fr/emploi/metier_tresorier-ville_fuveau-13710.html | Contexte: Hellowork signale offre(s) trésorier active(s) à Fuveau (13) au 02/09/2026. Zone industrielle Pays d'Aix (traitement déchets, matériaux, chimie, logistique). Signal J-1 très frais. Entreprise non identifiée (Hellowork bloqué proxy). À qualifier en priorité 1.</t>
+          <t>Poste: Gestionnaire de paie | Date: 2026-08-28 | Effectif: ~350 | CA: NC | Salaire: 30-36K€ | Source: LinkedIn Jobs | Lien: https://fr.linkedin.com/jobs/view/gestionnaire-de-paie-at-voyageurs-du-monde-2963369195 | Contexte: Leader français du voyage sur mesure fondé 1979, ~350 sal dont ~100 en régions. Recrute gestionnaire de paie CDI en équipe de 4 (paie+ADP), Paris 75, vu actif sur Indeed le 02/09/2026. Logiciel Sage, télétravail 2j/sem, participation, TR.</t>
         </is>
       </c>
     </row>
@@ -2096,28 +2853,28 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PME Bouches-du-Rhône (NC)</t>
+          <t>Voyageurs du Monde</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuveau (13)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Hellowork</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+          <t>LinkedIn Jobs / Indeed</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Poste: Trésorier | Date: 2026-09-02 | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (màj 02/09/2026) | Lien: https://www.hellowork.com/fr-fr/emploi/metier_tresorier-ville_fuveau-13710.html | Contexte: Idem contact 1. Fuveau (13). A traiter dès accès Hellowork rétabli.</t>
+          <t>Poste: Gestionnaire de paie | Date: 2026-08-28 | Effectif: ~350 | CA: NC | Salaire: 30-36K€ | Source: LinkedIn Jobs | Lien: https://fr.linkedin.com/jobs/view/gestionnaire-de-paie-at-voyageurs-du-monde-2963369195 | Contexte: Idem contact 1. DRH non identifié (site voyageursdumonde.fr bloqué proxy). Groupe privé 350 sal, Paris 75.</t>
         </is>
       </c>
     </row>
@@ -2128,33 +2885,33 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Responsable Finance / RAF</t>
+          <t>CEO / Fondateur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PME Gironde (NC)</t>
+          <t>Nextories</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bordeaux (33)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Hellowork</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>FINANCE,NEWS,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Poste: Trésorier | Date: 2026-08-30 | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (màj 30/08/2026) | Lien: https://www.hellowork.com/fr-fr/emploi/metier_tresorier-departement_gironde-33.html | Contexte: Hellowork recense offres trésorier actives en Gironde (33) au 30/08/2026. Bassin économique dynamique (industrie, négoce, agroalimentaire, viti). Entreprise non identifiée (Hellowork bloqué proxy). Signal dans la fenêtre 30j, à qualifier.</t>
+          <t>Poste: RAF (Responsable Administratif et Financier) | Date: NC | Effectif: NC (&lt;50 est.) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/nextories/jobs/responsable-administratif-et-financier-raf-h-f_paris | Contexte: Nextories, première plateforme professionnelle de déménagement B2B, recrute son RAF CDI Paris. Reporting direct CEO, structuration compta/tréso/social/fiscal. CEO/Fondateur non identifié (LinkedIn + WTJJ bloqués proxy).</t>
         </is>
       </c>
     </row>
@@ -2165,38 +2922,334 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DRH</t>
+          <t>DRH / Office Manager</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PME Gironde (NC)</t>
+          <t>Nextories</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bordeaux (33)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Poste: RAF (Responsable Administratif et Financier) | Date: NC | Effectif: NC (&lt;50 est.) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/nextories/jobs/responsable-administratif-et-financier-raf-h-f_paris | Contexte: Idem contact 1. Structure probablement &lt;50 sal, interlocuteur RH = CEO ou Office Manager. DRH formalisé peu probable à ce stade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>DAF / Directeur Financier</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Société industrielle - Somme (NC)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ailly-sur-Noye (80)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Hellowork (via Manpower)</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Poste: RAF (Responsable Administratif et Financier) | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (Manpower) | Lien: https://www.hellowork.com/fr-fr/emplois/50860822.html | Contexte: Site industriel en croissance dans la Somme (80) recrute un RAF CDI via Manpower. Entreprise cliente non identifiée (Hellowork bloqué proxy). Signal visible août 2026. Contacter Manpower Amiens pour qualifier le client final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Société industrielle - Somme (NC)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ailly-sur-Noye (80)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Hellowork (via Manpower)</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Poste: RAF (Responsable Administratif et Financier) | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (Manpower) | Lien: https://www.hellowork.com/fr-fr/emplois/50860822.html | Contexte: Idem contact 1. Industrial Somme (80). A prioriser dès identification du client Manpower.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DAF / Directeur Financier</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PME - Credit Manager Saint-Alban 31 (NC)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Saint-Alban (31)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Indeed France</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Poste: Credit Manager | Date: 2026-06 | Effectif: NC | CA: NC | Salaire: NC | Source: Indeed France | Lien: https://fr.indeed.com/q-credit-manager-emplois.html | Contexte: CDI Credit Manager basé au siège à Saint-Alban (31, Toulouse métropole). Missions: sécurisation risque clients, partenariat équipe commerciale, analyse financière, limites crédit, assurance-crédit, optimisation recouvrement. Entreprise non identifiée (Indeed bloqué proxy). Posting vu en juin 2026 sur Indeed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PME - Credit Manager Saint-Alban 31 (NC)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Saint-Alban (31)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Indeed France</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Poste: Credit Manager | Date: 2026-06 | Effectif: NC | CA: NC | Salaire: NC | Source: Indeed France | Lien: https://fr.indeed.com/q-credit-manager-emplois.html | Contexte: Idem contact 1. PME siège Saint-Alban (31). À qualifier en accédant Indeed ou en cherchant site:linkedin.com credit manager saint-alban 31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DAF / Trésorier</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PME Bouches-du-Rhône (NC)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fuveau (13)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,NEWS,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Poste: Trésorier | Date: 2026-09-02 | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (màj 02/09/2026) | Lien: https://www.hellowork.com/fr-fr/emploi/metier_tresorier-ville_fuveau-13710.html | Contexte: Hellowork signale offre(s) trésorier active(s) à Fuveau (13) au 02/09/2026. Zone industrielle Pays d'Aix (traitement déchets, matériaux, chimie, logistique). Signal J-1 très frais. Entreprise non identifiée (Hellowork bloqué proxy). À qualifier en priorité 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PME Bouches-du-Rhône (NC)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fuveau (13)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Hellowork</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>FINANCE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Poste: Trésorier | Date: 2026-09-02 | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (màj 02/09/2026) | Lien: https://www.hellowork.com/fr-fr/emploi/metier_tresorier-ville_fuveau-13710.html | Contexte: Idem contact 1. Fuveau (13). A traiter dès accès Hellowork rétabli.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Responsable Finance / RAF</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PME Gironde (NC)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bordeaux (33)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Hellowork</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,NEWS,DAF,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Poste: Trésorier | Date: 2026-08-30 | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (màj 30/08/2026) | Lien: https://www.hellowork.com/fr-fr/emploi/metier_tresorier-departement_gironde-33.html | Contexte: Hellowork recense offres trésorier actives en Gironde (33) au 30/08/2026. Bassin économique dynamique (industrie, négoce, agroalimentaire, viti). Entreprise non identifiée (Hellowork bloqué proxy). Signal dans la fenêtre 30j, à qualifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PME Gironde (NC)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bordeaux (33)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Hellowork</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>FINANCE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Poste: Trésorier | Date: 2026-08-30 | Effectif: NC | CA: NC | Salaire: NC | Source: Hellowork (màj 30/08/2026) | Lien: https://www.hellowork.com/fr-fr/emploi/metier_tresorier-departement_gironde-33.html | Contexte: Idem contact 1. Gironde (33). A prioriser dès accès France Travail ou Hellowork rétabli.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2210,9 +3263,9 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="41" customWidth="1" min="6" max="6"/>
@@ -2224,57 +3277,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>prenom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>poste</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>entreprise</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>localisation</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>linkedin</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -2298,7 +3351,7 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2327,7 +3380,7 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2356,7 +3409,7 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2385,7 +3438,7 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2414,7 +3467,7 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2443,7 +3496,7 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2472,7 +3525,7 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,PROPRIETAIRE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2501,7 +3554,7 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2530,7 +3583,7 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,PROPRIETAIRE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2559,7 +3612,7 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_SALLE,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2588,7 +3641,7 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2617,7 +3670,7 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2646,7 +3699,7 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2675,7 +3728,7 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2704,7 +3757,7 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2733,7 +3786,7 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2762,7 +3815,7 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2791,7 +3844,7 @@
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2820,7 +3873,7 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,PROPRIETAIRE,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2849,7 +3902,7 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2894,7 +3947,7 @@
           <t>Presse / Guide Michelin</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,CHEF_CUISINE,5-50,CONTACT_1</t>
         </is>
@@ -2923,7 +3976,7 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,GM,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -2952,7 +4005,7 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -2981,7 +4034,7 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3010,7 +4063,7 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3039,7 +4092,7 @@
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3068,7 +4121,7 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DIRECTEUR_HOTEL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3097,7 +4150,7 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3138,7 +4191,7 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DIRECTEUR_HOTEL,50-500,CONTACT_1</t>
         </is>
@@ -3179,7 +4232,7 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,PROPRIETAIRE,50-500,CONTACT_2</t>
         </is>
@@ -3208,7 +4261,7 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3237,7 +4290,7 @@
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3266,7 +4319,7 @@
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3295,7 +4348,7 @@
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3324,7 +4377,7 @@
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3353,7 +4406,7 @@
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3382,7 +4435,7 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,PROPRIETAIRE,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3411,7 +4464,7 @@
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3440,7 +4493,7 @@
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,GM,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3469,7 +4522,7 @@
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>HOSPITALITY,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3481,7 +4534,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3495,9 +4548,9 @@
   <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -3509,57 +4562,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>prenom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>telephone</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>poste</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>entreprise</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>localisation</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>linkedin</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -3599,7 +4652,7 @@
           <t>Mer et Marine</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,CEO,50-500,CONTACT_1</t>
         </is>
@@ -3636,7 +4689,7 @@
           <t>Mer et Marine</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3681,7 +4734,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,CEO,50-500,CONTACT_1</t>
         </is>
@@ -3718,7 +4771,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3755,7 +4808,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DIRECTEUR_GENERAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3792,7 +4845,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3829,7 +4882,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DIRECTEUR_GENERAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -3866,7 +4919,7 @@
           <t>Usine Nouvelle</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3915,7 +4968,7 @@
           <t>Usine Nouvelle / Partnaire</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DIRECTEUR_INDUSTRIEL,500-2000,CONTACT_1</t>
         </is>
@@ -3952,7 +5005,7 @@
           <t>Usine Nouvelle / Partnaire</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -3989,7 +5042,7 @@
           <t>Journal des Entreprises PDL</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DIRECTEUR_GENERAL,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4026,7 +5079,7 @@
           <t>Journal des Entreprises PDL</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,NEWS,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4063,7 +5116,7 @@
           <t>Indeed Bretagne</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4100,7 +5153,7 @@
           <t>Indeed Bretagne</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4137,7 +5190,7 @@
           <t>Indeed Bretagne</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4174,7 +5227,7 @@
           <t>Indeed Bretagne</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4211,7 +5264,7 @@
           <t>Indeed PDL</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4248,7 +5301,7 @@
           <t>Indeed PDL</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4285,7 +5338,7 @@
           <t>Indeed PDL</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4322,7 +5375,7 @@
           <t>Indeed PDL</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4359,7 +5412,7 @@
           <t>APEC Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4396,7 +5449,7 @@
           <t>APEC Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4433,7 +5486,7 @@
           <t>APEC Nouvelle-Aquitaine</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,RESP_QUALITE,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4470,7 +5523,7 @@
           <t>APEC Nouvelle-Aquitaine</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4507,7 +5560,7 @@
           <t>APEC Nouvelle-Aquitaine</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4544,7 +5597,7 @@
           <t>APEC Nouvelle-Aquitaine</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4581,7 +5634,7 @@
           <t>Indeed Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,RESP_MAINTENANCE,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4618,7 +5671,7 @@
           <t>Indeed Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4655,7 +5708,7 @@
           <t>Indeed Occitanie</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_SITE,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4692,7 +5745,7 @@
           <t>Indeed Occitanie</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4729,7 +5782,7 @@
           <t>APEC Grand Est</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_SITE,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4766,7 +5819,7 @@
           <t>APEC Grand Est</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4803,7 +5856,7 @@
           <t>APEC Grand Est</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4840,7 +5893,7 @@
           <t>APEC Grand Est</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4877,7 +5930,7 @@
           <t>Indeed Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4914,7 +5967,7 @@
           <t>Indeed Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -4951,7 +6004,7 @@
           <t>APEC Pays de la Loire</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DIRECTEUR_PRODUCTION,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -4988,7 +6041,7 @@
           <t>APEC Pays de la Loire</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -5025,7 +6078,7 @@
           <t>APEC Pays de la Loire</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,RESP_PRODUCTION,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
         </is>
@@ -5062,7 +6115,7 @@
           <t>APEC Pays de la Loire</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>INDUSTRIE,JOB,TALENT_ACQUISITION,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
         </is>
@@ -5074,7 +6127,3341 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>prenom</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>telephone</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>entreprise</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>localisation</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Guillet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cyril</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CEO &amp; cofondateur</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tenacy</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Lyon (69)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,50-500,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive Confirme/Senior (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: ~50-100 (2024) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/tenacy/jobs/account-executive-confirme-senior-cdi_lyon | Contexte: Editeur SaaS lyonnais de pilotage de la cybersecurite (fonde 2019). Serie A de 6 M EUR (Axeleo Capital, Auriga Cyber Ventures, Kreaxi, Teamwork, Credit Agricole Creation). Recrute 2 AE + 1 Inside Sales -&gt; structuration de l'equipe commerciale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Head of Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tenacy</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lyon (69)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive Confirme/Senior (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: ~50-100 (2024) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/tenacy/jobs/account-executive-confirme-senior-cdi_lyon | Contexte: Editeur SaaS lyonnais de pilotage de la cybersecurite (fonde 2019). Serie A de 6 M EUR (Axeleo Capital, Auriga Cyber Ventures, Kreaxi, Teamwork, Credit Agricole Creation). Recrute 2 AE + 1 Inside Sales -&gt; structuration de l'equipe commerciale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Santin</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Florent</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Co-CEO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>inwink</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,NC,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Poste: Partnership Manager - Martech SaaS BtoB (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/inwink/jobs/responsable-partenaires-inwink-cdi-h-f_paris | Contexte: Plateforme SaaS B2B d'evenementiel et d'engagement de communautes (groupe Infinite Square). Creation d'un poste de Responsable Partenaires : ouverture d'un canal indirect agences/editeurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Laforest</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pascal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Co-CEO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>inwink</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,NC,CONTACT_2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Poste: Partnership Manager - Martech SaaS BtoB (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/inwink/jobs/responsable-partenaires-inwink-cdi-h-f_paris | Contexte: Plateforme SaaS B2B d'evenementiel et d'engagement de communautes (groupe Infinite Square). Creation d'un poste de Responsable Partenaires : ouverture d'un canal indirect agences/editeurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Popote</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Damien</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CEO &amp; cofondateur</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mayday</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/damienpopote/</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,NC,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales (Product IA International) + Business Development Representative | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/mayday/jobs/head-of-sales-product-ia-international_paris | Contexte: Editeur SaaS de knowledge management pour services clients (Fnac Darty, EDF, Free). Rachete par le groupe allemand USU en septembre 2025 pour batir le leader europeen du KM : recrutement simultane d'un Head of Sales (8 ans+ SaaS Enterprise) et d'un BDR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Talent Acquisition / DRH</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mayday</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,NC,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Poste: Head of Sales (Product IA International) + Business Development Representative | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/mayday/jobs/head-of-sales-product-ia-international_paris | Contexte: Editeur SaaS de knowledge management pour services clients (Fnac Darty, EDF, Free). Rachete par le groupe allemand USU en septembre 2025 pour batir le leader europeen du KM : recrutement simultane d'un Head of Sales (8 ans+ SaaS Enterprise) et d'un BDR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fort</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Antoine</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CEO &amp; cofondateur</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Qobra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antoine-fort/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,NC,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager Onboarding (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: ~8 M$ ARR (source getlatka) | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/en/companies/qobra/jobs/customer-success-manager-onboarding-cdi-paris_paris | Contexte: Editeur SaaS de sales compensation (commissionnement temps reel), 350+ clients, adosse a Singular et Breega. Equipe CS de 8 personnes en extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Talent Acquisition / DRH</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Qobra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,NC,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager Onboarding (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: ~8 M$ ARR (source getlatka) | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/en/companies/qobra/jobs/customer-success-manager-onboarding-cdi-paris_paris | Contexte: Editeur SaaS de sales compensation (commissionnement temps reel), 350+ clients, adosse a Singular et Breega. Equipe CS de 8 personnes en extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dubouloz</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CEO &amp; fondateur</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>N2JSoft (N2F)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lyon (69)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,50-500,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Poste: Sales Enablement Manager B2B SaaS + Revenue Operations Manager | Date: NC (annonce en ligne au 2026-09-03) | Effectif: 130 (2024) | CA: &gt;10 M EUR (2023, +60%) | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/n2jsoft-fr/jobs/sales-enablement-manager-b2b-saas_lyon_N2JSO_1P47kww | Contexte: Editeur SaaS de gestion des notes de frais (N2F) : 16 000 clients, 90 pays. Effectif passe de 70 a 130 en un an. Recrute Sales Enablement + RevOps + SDR : structuration complete de la machine commerciale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Talent Acquisition / DRH</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>N2JSoft (N2F)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lyon (69)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Poste: Sales Enablement Manager B2B SaaS + Revenue Operations Manager | Date: NC (annonce en ligne au 2026-09-03) | Effectif: 130 (2024) | CA: &gt;10 M EUR (2023, +60%) | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/n2jsoft-fr/jobs/sales-enablement-manager-b2b-saas_lyon_N2JSO_1P47kww | Contexte: Editeur SaaS de gestion des notes de frais (N2F) : 16 000 clients, 90 pays. Effectif passe de 70 a 130 en un an. Recrute Sales Enablement + RevOps + SDR : structuration complete de la machine commerciale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Trouche</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Maxime</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cofondateur &amp; CEO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Reecall</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lyon (69)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,NC,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Poste: Sales Development Representative (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/reecall/jobs/business-developer_paris | Contexte: Editeur d'agents vocaux IA pour la relation client (Lyon &amp; Paris, cree en 2019). Recrute un SDR pour accelerer la croissance sur les cibles PME/ETI e-commerce, SaaS et assurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Szymocha</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cofondateur</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Reecall</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lyon (69)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,FONDATEUR,NC,CONTACT_2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Poste: Sales Development Representative (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/reecall/jobs/business-developer_paris | Contexte: Editeur d'agents vocaux IA pour la relation client (Lyon &amp; Paris, cree en 2019). Recrute un SDR pour accelerer la croissance sur les cibles PME/ETI e-commerce, SaaS et assurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ristagno</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CEO &amp; cofondateur</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Uptale</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,NC,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Poste: B2B Account Executive (AI &amp; Immersive Learning) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/uptale/jobs/sales-development-representative-sdr-education-secteur-public_tunis | Contexte: Plateforme SaaS d'immersive learning (VR/AR) utilisee par 75% du CAC40 et par Harvard. Levee de 9 M EUR fin 2024, recrute des AE B2B pour couvrir l'international.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Iserief</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dwayne</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CMO &amp; cofondateur</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Uptale</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,FONDATEUR,NC,CONTACT_2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Poste: B2B Account Executive (AI &amp; Immersive Learning) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/uptale/jobs/sales-development-representative-sdr-education-secteur-public_tunis | Contexte: Plateforme SaaS d'immersive learning (VR/AR) utilisee par 75% du CAC40 et par Harvard. Levee de 9 M EUR fin 2024, recrute des AE B2B pour couvrir l'international.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Delorme</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stephane</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cofondateur</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>A World For Us (Digiforma)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,FONDATEUR,NC,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive (Sales &amp; Customer Success) - Digiforma Certif | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/a-world-for-us/jobs/account-executive-sales-customer-success-digiforma-certif-h-f-edtech-saas_paris | Contexte: Editeur SaaS EdTech (Digiforma) pour organismes de formation, autofinance (aucun fonds au capital). Vient de prendre une participation majoritaire dans l'editeur Rich-ID (certifications pro) : nouvelle ligne produit Digiforma Certif a commercialiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Talent Acquisition / DRH</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>A World For Us (Digiforma)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,NC,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive (Sales &amp; Customer Success) - Digiforma Certif | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/a-world-for-us/jobs/account-executive-sales-customer-success-digiforma-certif-h-f-edtech-saas_paris | Contexte: Editeur SaaS EdTech (Digiforma) pour organismes de formation, autofinance (aucun fonds au capital). Vient de prendre une participation majoritaire dans l'editeur Rich-ID (certifications pro) : nouvelle ligne produit Digiforma Certif a commercialiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Larrain</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Eduardo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fondateur &amp; CEO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kel Foncier</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,50-500,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager / Charge de relation client B2B (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: ~50 | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/kel-foncier/jobs/customer-success-manager-charge-de-relation-client-b2b-h-f_paris | Contexte: Editeur SaaS data &amp; analytics du foncier pour promoteurs immobiliers et energies renouvelables (cree en 2010, laureat Pass French Tech). Renforce l'equipe relation client B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Talent Acquisition / DRH</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kel Foncier</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager / Charge de relation client B2B (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: ~50 | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/kel-foncier/jobs/customer-success-manager-charge-de-relation-client-b2b-h-f_paris | Contexte: Editeur SaaS data &amp; analytics du foncier pour promoteurs immobiliers et energies renouvelables (cree en 2010, laureat Pass French Tech). Renforce l'equipe relation client B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CEO &amp; cofondateur</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Novalend Tech Solutions</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Puteaux (92)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager - Solutions SaaS Leasing B2B | Date: NC (annonce en ligne au 2026-09-03) | Effectif: 19 (2026) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/novalend-fr/jobs/customer-success-manager-h-f-solutions-saas-leasing-b2b_puteaux_NTS_031Xk7K | Contexte: Editeur SaaS pour les acteurs du leasing B2B (banques, brokers, industriels), cree en 2020. Premier recrutement CSM structurant sur une equipe de moins de 20 personnes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DRH / Office Manager</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Novalend Tech Solutions</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Puteaux (92)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager - Solutions SaaS Leasing B2B | Date: NC (annonce en ligne au 2026-09-03) | Effectif: 19 (2026) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/novalend-fr/jobs/customer-success-manager-h-f-solutions-saas-leasing-b2b_puteaux_NTS_031Xk7K | Contexte: Editeur SaaS pour les acteurs du leasing B2B (banques, brokers, industriels), cree en 2020. Premier recrutement CSM structurant sur une equipe de moins de 20 personnes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Philibin</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Julien</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Fondateur</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Modulotech</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Issy-les-Moulineaux (92)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,FONDATEUR,5-50,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: 20-49 (2023) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/modulotech/jobs/customer-success-manager_issy-les-moulineaux | Contexte: Editeur de logiciel de gestion des interventions terrain (cree 2011). Creation from scratch de la fonction Customer Success : premier CSM de la societe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DRH / Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Modulotech</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Issy-les-Moulineaux (92)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: 20-49 (2023) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/modulotech/jobs/customer-success-manager_issy-les-moulineaux | Contexte: Editeur de logiciel de gestion des interventions terrain (cree 2011). Creation from scratch de la fonction Customer Success : premier CSM de la societe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Moinard</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Cofondateur &amp; CEO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Localranker</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicolas-moinard/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,5-50,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager Grands Comptes (SaaS B2B) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: ~10 | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/localranker/jobs/account-manager-grands-comptes-strategic-customer-success-manager-saas-b2b_paris | Contexte: Solution SaaS tout-en-un de SEO local pour reseaux de points de vente (8 000 points de vente : Century 21, Continental, Mister Menuiserie). Ouvre un poste Grands Comptes : montee en gamme du portefeuille.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jamey</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cofondateur &amp; CMO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Localranker</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jamey-lee/</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,FONDATEUR,5-50,CONTACT_2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager Grands Comptes (SaaS B2B) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: ~10 | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/localranker/jobs/account-manager-grands-comptes-strategic-customer-success-manager-saas-b2b_paris | Contexte: Solution SaaS tout-en-un de SEO local pour reseaux de points de vente (8 000 points de vente : Century 21, Continental, Mister Menuiserie). Ouvre un poste Grands Comptes : montee en gamme du portefeuille.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Huraux</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ludovic</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cofondateur &amp; CEO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Shapr</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,NC,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager B2B - SaaS (2 postes) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/shapr/jobs/customer-success-manager-b2b-saas_paris_SHAPR_AWZyVDQ | Contexte: Plateforme de mise en relation professionnelle en bascule vers une offre B2B (14,8 M EUR leves au total). Deux postes CSM B2B SaaS ouverts en parallele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bobin</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Vincent</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cofondateur</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Shapr</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,FONDATEUR,NC,CONTACT_2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Poste: Customer Success Manager B2B - SaaS (2 postes) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/shapr/jobs/customer-success-manager-b2b-saas_paris_SHAPR_AWZyVDQ | Contexte: Plateforme de mise en relation professionnelle en bascule vers une offre B2B (14,8 M EUR leves au total). Deux postes CSM B2B SaaS ouverts en parallele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ducret</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Frank</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CEO &amp; fondateur</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Agnostik</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,CEO,5-50,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive - Logiciel SaaS Privacy Tech (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC (groupe Didomi ~200) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/agnostik/jobs/account-executive-cdi-logiciel-saas-privacy-tech_paris | Contexte: Editeur SaaS Privacy Tech (conformite RGPD/CNIL) pour medias et e-commerce, adosse au groupe Didomi depuis 2022. Recrute un AE sur l'offre logicielle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Talent Acquisition / DRH</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Agnostik</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,JOB,TALENT_ACQUISITION,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Poste: Account Executive - Logiciel SaaS Privacy Tech (CDI) | Date: NC (annonce en ligne au 2026-09-03) | Effectif: NC (groupe Didomi ~200) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/agnostik/jobs/account-executive-cdi-logiciel-saas-privacy-tech_paris | Contexte: Editeur SaaS Privacy Tech (conformite RGPD/CNIL) pour medias et e-commerce, adosse au groupe Didomi depuis 2022. Recrute un AE sur l'offre logicielle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Directeur General</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MyUnisoft</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Saint-Quentin-en-Yvelines (78)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ChannelNews</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,DG,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Poste: Plan de recrutement 100 postes 2026 | Date: 2026 (mois non confirme) | Effectif: 253 -&gt; 353 vise fin 2026 | CA: NC | Salaire: NC | Source: ChannelNews | Lien: https://www.channelnews.fr/myunisoft-annonce-100-recrutements-en-2026-155383 | Contexte: Editeur SaaS de comptabilite (1 300 cabinets, 250 000 TPE/PME). Annonce 100 recrutements en 2026 pour passer de 253 a 353 salaries. Majorite des postes a Saint-Quentin-en-Yvelines, une dizaine a Toulouse. Actionnaire majoritaire depuis decembre : HgCapital, aux cotes de 125 cabinets d'expertise comptable actionnaires. | Fonds: HgCapital | Montant: NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DRH / Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MyUnisoft</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Saint-Quentin-en-Yvelines (78)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ChannelNews</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Poste: Plan de recrutement 100 postes 2026 | Date: 2026 (mois non confirme) | Effectif: 253 -&gt; 353 vise fin 2026 | CA: NC | Salaire: NC | Source: ChannelNews | Lien: https://www.channelnews.fr/myunisoft-annonce-100-recrutements-en-2026-155383 | Contexte: Editeur SaaS de comptabilite (1 300 cabinets, 250 000 TPE/PME). Annonce 100 recrutements en 2026 pour passer de 253 a 353 salaries. Majorite des postes a Saint-Quentin-en-Yvelines, une dizaine a Toulouse. Actionnaire majoritaire depuis decembre : HgCapital, aux cotes de 125 cabinets d'expertise comptable actionnaires. | Fonds: HgCapital | Montant: NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CEO / Directeur General</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>padoa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Thoma Bravo (communique) / Kirkland &amp; Ellis</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,CEO,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Poste: Prise de participation majoritaire | Date: 2026-07 (finalisation) | Effectif: NC (~400) | CA: NC | Salaire: NC | Source: Thoma Bravo | Lien: https://www.thomabravo.com/press-releases/thoma-bravo-completes-acquisition-of-padoa | Contexte: Editeur SaaS leader europeen de la sante et prevention au travail (SPST), fonde en 2016 chez Kamet Ventures. Thoma Bravo prend une participation majoritaire via son fonds Europe de 1,8 Md EUR | Five Arrows (Rothschild &amp; Co) et Kamet restent au capital. Plan : expansion internationale (DACH) et investissement produit/IA -&gt; recrutements commerciaux attendus. | Fonds: Thoma Bravo (fonds Europe 1|8 Md EUR) | Montant: NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DRH / Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>padoa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Thoma Bravo (communique) / Kirkland &amp; Ellis</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Poste: Prise de participation majoritaire | Date: 2026-07 (finalisation) | Effectif: NC (~400) | CA: NC | Salaire: NC | Source: Thoma Bravo | Lien: https://www.thomabravo.com/press-releases/thoma-bravo-completes-acquisition-of-padoa | Contexte: Editeur SaaS leader europeen de la sante et prevention au travail (SPST), fonde en 2016 chez Kamet Ventures. Thoma Bravo prend une participation majoritaire via son fonds Europe de 1,8 Md EUR | Five Arrows (Rothschild &amp; Co) et Kamet restent au capital. Plan : expansion internationale (DACH) et investissement produit/IA -&gt; recrutements commerciaux attendus. | Fonds: Thoma Bravo (fonds Europe 1|8 Md EUR) | Montant: NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CEO / Cofondateur</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Aria</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>EU-Startups</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,CEO,NC,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Poste: Levee 7 M EUR + facilite de dette 240 M EUR | Date: 2026-07 | Effectif: NC | CA: NC | Salaire: NC | Source: EU-Startups | Lien: https://www.eu-startups.com/2026/07/paris-based-aria-raises-e7-million-and-launches-e240-million-debt-facility-to-tackle-europes-late-payment-crisis/ | Contexte: Fintech B2B parisienne de financement de factures embarque (embedded invoice financing). Leve 7 M EUR en equity et ouvre une facilite de dette de 240 M EUR pour attaquer le probleme des retards de paiement en Europe : phase de deploiement commercial paneuropeen. | Fonds: NC | Montant: 7 M EUR equity + 240 M EUR de dette</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DRH / Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Aria</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EU-Startups</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,DRH,NC,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Poste: Levee 7 M EUR + facilite de dette 240 M EUR | Date: 2026-07 | Effectif: NC | CA: NC | Salaire: NC | Source: EU-Startups | Lien: https://www.eu-startups.com/2026/07/paris-based-aria-raises-e7-million-and-launches-e240-million-debt-facility-to-tackle-europes-late-payment-crisis/ | Contexte: Fintech B2B parisienne de financement de factures embarque (embedded invoice financing). Leve 7 M EUR en equity et ouvre une facilite de dette de 240 M EUR pour attaquer le probleme des retards de paiement en Europe : phase de deploiement commercial paneuropeen. | Fonds: NC | Montant: 7 M EUR equity + 240 M EUR de dette</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CEO / Cofondateur</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vocca</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>The SaaS News</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,CEO,NC,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Poste: Levee seed 5,5 M$ | Date: 2026-08-11 | Effectif: NC | CA: NC | Salaire: NC | Source: The SaaS News | Lien: https://www.thesaasnews.com/news/vocca-raises-5-5-million-in-seed-round/ | Contexte: Startup parisienne de voice AI appliquee a la sante (automatisation de l'accueil telephonique des cabinets et structures de soins). Tour de seed de 5,5 M$ boucle le 11 aout 2026 : phase classique de constitution d'une premiere equipe sales/CS. | Fonds: NC | Montant: 5,5 M$</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DRH / Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vocca</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>The SaaS News</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,DRH,NC,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Poste: Levee seed 5,5 M$ | Date: 2026-08-11 | Effectif: NC | CA: NC | Salaire: NC | Source: The SaaS News | Lien: https://www.thesaasnews.com/news/vocca-raises-5-5-million-in-seed-round/ | Contexte: Startup parisienne de voice AI appliquee a la sante (automatisation de l'accueil telephonique des cabinets et structures de soins). Tour de seed de 5,5 M$ boucle le 11 aout 2026 : phase classique de constitution d'une premiere equipe sales/CS. | Fonds: NC | Montant: 5,5 M$</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guiraud</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Laurent</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cofondateur</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ColibriTD</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>EU-Startups</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,FONDATEUR,5-50,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Poste: Levee seed 4 M EUR | Date: 2026-08-27 | Effectif: NC | CA: NC | Salaire: NC | Source: EU-Startups | Lien: https://www.eu-startups.com/2026/08/paris-based-colibritd-raises-e4-million-to-scale-its-quantum-powered-multiphysics-simulation-platform | Contexte: Editeur deeptech B2B parisien (fonde 2019) d'une plateforme de simulation multiphysique acceleree par le calcul quantique. Seed de 4 M EUR menee par Earlybird Venture Capital avec SymbiaVC et Medin VC, pour passer a l'echelle commerciale (industrie, energie, aeronautique). | Fonds: Earlybird Venture Capital (lead) | SymbiaVC | Medin VC | Montant: 4 M EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Goudjil</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hacene</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cofondateur</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ColibriTD</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>EU-Startups</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,FONDATEUR,5-50,CONTACT_2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Poste: Levee seed 4 M EUR | Date: 2026-08-27 | Effectif: NC | CA: NC | Salaire: NC | Source: EU-Startups | Lien: https://www.eu-startups.com/2026/08/paris-based-colibritd-raises-e4-million-to-scale-its-quantum-powered-multiphysics-simulation-platform | Contexte: Editeur deeptech B2B parisien (fonde 2019) d'une plateforme de simulation multiphysique acceleree par le calcul quantique. Seed de 4 M EUR menee par Earlybird Venture Capital avec SymbiaVC et Medin VC, pour passer a l'echelle commerciale (industrie, energie, aeronautique). | Fonds: Earlybird Venture Capital (lead) | SymbiaVC | Medin VC | Montant: 4 M EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CEO / Directeur General</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Innovorder</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EU-Startups</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,CEO,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Poste: Levee 20 M EUR | Date: 2026-06 | Effectif: NC (~150) | CA: NC | Salaire: NC | Source: EU-Startups | Lien: https://www.eu-startups.com/2026/06/profitable-french-scale-up-innovorder-raises-e20-million-to-accelerate-ai-first-restaurant-digitalisation/ | Contexte: Scale-up SaaS rentable de digitalisation de la restauration (caisse, commande, back-office). Leve 20 M EUR pour accelerer sa bascule AI-first : signal de croissance commerciale, hors fenetre 30 jours (juin 2026) mais operation recente et societe non surmediatisee. | Fonds: NC | Montant: 20 M EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DRH / Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Innovorder</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>EU-Startups</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>SALES_SAAS,NEWS,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Poste: Levee 20 M EUR | Date: 2026-06 | Effectif: NC (~150) | CA: NC | Salaire: NC | Source: EU-Startups | Lien: https://www.eu-startups.com/2026/06/profitable-french-scale-up-innovorder-raises-e20-million-to-accelerate-ai-first-restaurant-digitalisation/ | Contexte: Scale-up SaaS rentable de digitalisation de la restauration (caisse, commande, back-office). Leve 20 M EUR pour accelerer sa bascule AI-first : signal de croissance commerciale, hors fenetre 30 jours (juin 2026) mais operation recente et societe non surmediatisee. | Fonds: NC | Montant: 20 M EUR</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>prenom</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>telephone</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>poste</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>entreprise</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>localisation</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SAIREM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Décines-Charpieu (69)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Agroalimentaire | Date: NC | Effectif: 100-199 salariés | CA: 25 M€ (2023) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-agroalimentaire-at-sairem-4138889507 | Contexte: Leader européen des solutions industrielles micro-ondes et radiofréquences (agroalimentaire, chimie) | recrute un responsable commercial dédié au secteur agroalimentaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SAIREM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Décines-Charpieu (69)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Agroalimentaire | Date: NC | Effectif: 100-199 salariés | CA: 25 M€ (2023) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-agroalimentaire-at-sairem-4138889507 | Contexte: Leader européen des solutions industrielles micro-ondes et radiofréquences (agroalimentaire, chimie) | recrute un responsable commercial dédié au secteur agroalimentaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Responsable Commercial Régional</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ZEP Industries</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Albi (81)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial BtoB H/F - Albi | Date: NC | Effectif: 100-499 salariés (siège Nogent-le-Roi 28) | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-btob-h-f-albi-at-zep-industries-3357527121 | Contexte: Fabricant français (ISO 9001, French Fab) de produits de nettoyage et maintenance pro pour l'industrie/agroalimentaire | plus de 150 commerciaux terrain en France, poursuit ses recrutements régionaux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ZEP Industries</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Albi (81)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial BtoB H/F - Albi | Date: NC | Effectif: 100-499 salariés (siège Nogent-le-Roi 28) | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-btob-h-f-albi-at-zep-industries-3357527121 | Contexte: Fabricant français (ISO 9001, French Fab) de produits de nettoyage et maintenance pro pour l'industrie/agroalimentaire | plus de 150 commerciaux terrain en France, poursuit ses recrutements régionaux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Krampouz</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pluguffan (29)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Poste: Commercial(e) IDF, Centre, Haute-Normandie F/H | Date: NC | Effectif: 100-199 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/commercial-e-idf-centre-haute-normandie-f-h-at-krampouz-3272539245 | Contexte: Fabricant breton historique de crêpières et matériel de cuisson pro/grand public, exporté dans 160 pays | recrute plusieurs commerciaux régionaux (autres postes ouverts: Nord-Est, International).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Krampouz</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pluguffan (29)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Poste: Commercial(e) IDF, Centre, Haute-Normandie F/H | Date: NC | Effectif: 100-199 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/commercial-e-idf-centre-haute-normandie-f-h-at-krampouz-3272539245 | Contexte: Fabricant breton historique de crêpières et matériel de cuisson pro/grand public, exporté dans 160 pays | recrute plusieurs commerciaux régionaux (autres postes ouverts: Nord-Est, International).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAJDLER</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Luc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Responsable Développement Commercial</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Transports Caillot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bétheny (51)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luc-cajdler-562321162/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>SALES,JOB,HIRING_MANAGER,500-2000,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Transport et Logistique | Date: NC | Effectif: 500-999 salariés | CA: 76 M€ (2023) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-transport-et-logistique-at-transports-caillot-3952223846 | Contexte: Transporteur routier familial (Groupe Caillot), 15 établissements en France | recrute un responsable commercial transport/logistique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Transports Caillot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bétheny (51)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Transport et Logistique | Date: NC | Effectif: 500-999 salariés | CA: 76 M€ (2023) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-transport-et-logistique-at-transports-caillot-3952223846 | Contexte: Transporteur routier familial (Groupe Caillot), 15 établissements en France | recrute un responsable commercial transport/logistique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SAS Transports Van de Walle</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Issoudun (36)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Transport et Logistique | Date: NC | Effectif: 200-249 salariés | CA: 26,8 M€ (2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-transport-et-logistique-at-sas-transports-van-de-walle-3997310360 | Contexte: Transporteur routier indépendant fondé en 1985 (transport interurbain de marchandises) | recrute un responsable commercial transport/logistique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SAS Transports Van de Walle</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Issoudun (36)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Transport et Logistique | Date: NC | Effectif: 200-249 salariés | CA: 26,8 M€ (2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-transport-et-logistique-at-sas-transports-van-de-walle-3997310360 | Contexte: Transporteur routier indépendant fondé en 1985 (transport interurbain de marchandises) | recrute un responsable commercial transport/logistique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Heliowatt Construction</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vendargues (34)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DG,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Poste: Chargé/Chargée d'affaires BTP | Date: NC | Effectif: 20-49 salariés | CA: 5,58 M€ (30/09/2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/charg%C3%A9-charg%C3%A9e-d-affaires-btp-at-heliowatt-construction-3716741950 | Contexte: PME de construction de centrales photovoltaïques et structures métalliques (Hérault) | recrute un chargé d'affaires pour développer le portefeuille clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Responsable Administratif et Financier</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Heliowatt Construction</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Vendargues (34)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DAF,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Poste: Chargé/Chargée d'affaires BTP | Date: NC | Effectif: 20-49 salariés | CA: 5,58 M€ (30/09/2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/charg%C3%A9-charg%C3%A9e-d-affaires-btp-at-heliowatt-construction-3716741950 | Contexte: PME de construction de centrales photovoltaïques et structures métalliques (Hérault) | recrute un chargé d'affaires pour développer le portefeuille clients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Champagne Henriot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Reims (51)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DG,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial France | Date: NC | Effectif: 20-49 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-france-at-champagne-henriot-4439889741 | Contexte: Maison de Champagne familiale et indépendante fondée en 1808, 30 ha de vignoble en propre | recrute un responsable commercial pour le marché France.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Champagne Henriot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Reims (51)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial France | Date: NC | Effectif: 20-49 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-france-at-champagne-henriot-4439889741 | Contexte: Maison de Champagne familiale et indépendante fondée en 1808, 30 ha de vignoble en propre | recrute un responsable commercial pour le marché France.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Directeur Général</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Warmpac France</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vitrolles (13)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DG,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Poste: Technico-Commercial H/F | Date: NC | Effectif: 20-49 salariés (famille: 27 en France + 5 en Asie) | CA: 6,94 M€ (30/09/2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-h-f-at-warmpac-3460410522 | Contexte: Fabricant/distributeur familial de pompes à chaleur piscine (marque WPool), leader du secteur | multiplie les postes technico-commerciaux régionaux (plusieurs zones ouvertes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Responsable Administratif et Financier</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Warmpac France</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vitrolles (13)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DAF,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Poste: Technico-Commercial H/F | Date: NC | Effectif: 20-49 salariés (famille: 27 en France + 5 en Asie) | CA: 6,94 M€ (30/09/2024) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-h-f-at-warmpac-3460410522 | Contexte: Fabricant/distributeur familial de pompes à chaleur piscine (marque WPool), leader du secteur | multiplie les postes technico-commerciaux régionaux (plusieurs zones ouvertes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CHAPOUTIER</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Michel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Président / Dirigeant</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>M. Chapoutier</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tain-l'Hermitage (26)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Indeed / Vitijob</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>SALES,JOB,FONDATEUR,50-500,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Régional des Ventes et Commercial Exclusif (H/F) / Commercial CHR Rhône (vins) | Date: 2026-07-28 | Effectif: 68 salariés (maison) / ~300 salariés (groupe, incl. activités oeno-tourisme et restauration) | CA: NC | Salaire: NC | Source: Indeed / Vitijob | Lien: https://www.vitijob.com/emploi/societe/1478/groupe-m-chapoutier | Contexte: Maison de vins familiale indépendante (biodynamie, AOC Côtes du Rhône), 14 établissements | plusieurs postes commerciaux ouverts (vente directe CHR, export). Date de publication antérieure à 7 jours - fraîcheur exacte non garantie, à vérifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>M. Chapoutier</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tain-l'Hermitage (26)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Indeed / Vitijob</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Régional des Ventes et Commercial Exclusif (H/F) / Commercial CHR Rhône (vins) | Date: 2026-07-28 | Effectif: 68 salariés (maison) / ~300 salariés (groupe, incl. activités oeno-tourisme et restauration) | CA: NC | Salaire: NC | Source: Indeed / Vitijob | Lien: https://www.vitijob.com/emploi/societe/1478/groupe-m-chapoutier | Contexte: Maison de vins familiale indépendante (biodynamie, AOC Côtes du Rhône), 14 établissements | plusieurs postes commerciaux ouverts (vente directe CHR, export). Date de publication antérieure à 7 jours - fraîcheur exacte non garantie, à vérifier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Foussier</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Toulouse (31)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Poste: Technico-Commercial | Date: NC | Effectif: 1000-1999 salariés (siège Allonnes, 72) | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-at-foussier-3428568921 | Contexte: Distributeur indépendant de fournitures techniques quincaillerie/bâtiment/industrie, 85 agences actives en France | recrute des technico-commerciaux dans plusieurs régions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Foussier</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Toulouse (31)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Poste: Technico-Commercial | Date: NC | Effectif: 1000-1999 salariés (siège Allonnes, 72) | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-at-foussier-3428568921 | Contexte: Distributeur indépendant de fournitures techniques quincaillerie/bâtiment/industrie, 85 agences actives en France | recrute des technico-commerciaux dans plusieurs régions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>LSO Medical</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Loos (59)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Dispositifs Médicaux - France Zone Ouest / Zone Nord | Date: NC | Effectif: 20-49 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-dispositifs-m%C3%A9dicaux-france-zone-ouest-h-f-at-lso-medical-3424284556 | Contexte: PME française fondée en 2002, conception/fabrication de lasers médicaux (traitement des varices) | recrute plusieurs responsables commerciaux régionaux, rattachés au Directeur Commercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>LSO Medical</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Loos (59)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Dispositifs Médicaux - France Zone Ouest / Zone Nord | Date: NC | Effectif: 20-49 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-dispositifs-m%C3%A9dicaux-france-zone-ouest-h-f-at-lso-medical-3424284556 | Contexte: PME française fondée en 2002, conception/fabrication de lasers médicaux (traitement des varices) | recrute plusieurs responsables commerciaux régionaux, rattachés au Directeur Commercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Directeur Commercial</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Groupe Derval Rogé</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bologne (52)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial en Matériel Agricole | Date: NC | Effectif: ~60 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-en-mat%C3%A9riel-agricole-at-groupe-derval-rog%C3%A9-4444921001 | Contexte: Concessionnaire agricole indépendant (marques JCB, Fendt, Valtra, Holmer), 6 bases dans l'Aube/Marne/Haute-Marne | recrute un responsable commercial matériel agricole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Responsable Administratif et Financier</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Groupe Derval Rogé</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bologne (52)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DAF,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial en Matériel Agricole | Date: NC | Effectif: ~60 salariés | CA: NC | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/responsable-commercial-en-mat%C3%A9riel-agricole-at-groupe-derval-rog%C3%A9-4444921001 | Contexte: Concessionnaire agricole indépendant (marques JCB, Fendt, Valtra, Holmer), 6 bases dans l'Aube/Marne/Haute-Marne | recrute un responsable commercial matériel agricole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PANAGET</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Yves</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Fondateur &amp; Président</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Design Parquet</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Torcé (35)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>SALES,JOB,FONDATEUR,50-500,CONTACT_1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial / Responsable des ventes Sud-Ouest H/F | Date: NC | Effectif: ~250 salariés (France) + filiale Roumanie | CA: 34 M€ (2022) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-responsable-des-ventes-sud-ouest-h-f-at-design-parquet-france-4437197376 | Contexte: Fabricant familial breton de parquets (Top 3 France), en croissance de 15% sur 3 ans, nouvel investissement industriel prévu | recrute un responsable des ventes zone Sud-Ouest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Responsable RH</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Design Parquet</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Torcé (35)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial / Responsable des ventes Sud-Ouest H/F | Date: NC | Effectif: ~250 salariés (France) + filiale Roumanie | CA: 34 M€ (2022) | Salaire: NC | Source: LinkedIn | Lien: https://fr.linkedin.com/jobs/view/technico-commercial-responsable-des-ventes-sud-ouest-h-f-at-design-parquet-france-4437197376 | Contexte: Fabricant familial breton de parquets (Top 3 France), en croissance de 15% sur 3 ans, nouvel investissement industriel prévu | recrute un responsable des ventes zone Sud-Ouest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Directeur commercial</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Groupe Derrey</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Epinal (88)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Site carriere Derrey</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial H/F CDI | Date: NC | Effectif: 600 | CA: NC | Salaire: NC | Source: Site carriere Derrey + Le Journal des Entreprises | Lien: https://groupe.derrey.fr/job/technico-commercial-h-f-en-cdi-epinal/ | Contexte: Negoce de materiaux de construction et fabrication de betons | siege Etival-Clairefontaine (88) | 600 salaries. Campagne de 26 postes en CDI dans le Grand Est (commerce| logistique| supports) sur Colmar| Hilsenheim| Reichstett| Epinal| Luneville| Laneuveville| Etival-Clairefontaine. Groupe familial independant| poste technico-commercial ouvert a Epinal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Groupe Derrey</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Epinal (88)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Site carriere Derrey</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Poste: Technico-commercial H/F CDI | Date: NC | Effectif: 600 | CA: NC | Salaire: NC | Source: Site carriere Derrey + Le Journal des Entreprises | Lien: https://groupe.derrey.fr/job/technico-commercial-h-f-en-cdi-epinal/ | Contexte: Negoce de materiaux de construction et fabrication de betons | siege Etival-Clairefontaine (88) | 600 salaries. Campagne de 26 postes en CDI dans le Grand Est (commerce| logistique| supports) sur Colmar| Hilsenheim| Reichstett| Epinal| Luneville| Laneuveville| Etival-Clairefontaine. Groupe familial independant| poste technico-commercial ouvert a Epinal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Directeur commercial France</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Chauvin Arnoux</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Toulouse (31)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Poste: Ingenieur Technico-commercial H/F CDI | Date: NC | Effectif: 430 | CA: 57 M EUR (2024) | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/chauvin-arnoux/jobs/ingenieur-technico-commercial-h-f_toulouse | Contexte: Groupe francais independant et familial d'instrumentation de mesure et de test (siege Asnieres-sur-Seine| 11 etablissements| filiales US/Chine/Europe). Recrute un ingenieur technico-commercial itinerant sur la zone Toulouse| avec vehicule de fonction et perspectives d'evolution. 11% du CA reinvesti en R&amp;D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Chauvin Arnoux</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Toulouse (31)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Poste: Ingenieur Technico-commercial H/F CDI | Date: NC | Effectif: 430 | CA: 57 M EUR (2024) | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/chauvin-arnoux/jobs/ingenieur-technico-commercial-h-f_toulouse | Contexte: Groupe francais independant et familial d'instrumentation de mesure et de test (siege Asnieres-sur-Seine| 11 etablissements| filiales US/Chine/Europe). Recrute un ingenieur technico-commercial itinerant sur la zone Toulouse| avec vehicule de fonction et perspectives d'evolution. 11% du CA reinvesti en R&amp;D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Directeur commercial / Head of Sales</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Castalie</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nantes (44)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,HEAD_OF_SALES,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Poste: Business Developer Grand Ouest F/H CDI | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/castalie/jobs/business-developer-grand-ouest-f-h_nantes | Contexte: Fabricant-operateur de fontaines a eau micro-filtree en B2B (CHR| entreprises| collectivites)| entreprise a mission. Creation/renfort d'un poste de business developer dedie au Grand Ouest base a Nantes| profil 3-5 ans d'experience vente B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Castalie</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nantes (44)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,TALENT_ACQUISITION,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Poste: Business Developer Grand Ouest F/H CDI | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/castalie/jobs/business-developer-grand-ouest-f-h_nantes | Contexte: Fabricant-operateur de fontaines a eau micro-filtree en B2B (CHR| entreprises| collectivites)| entreprise a mission. Creation/renfort d'un poste de business developer dedie au Grand Ouest base a Nantes| profil 3-5 ans d'experience vente B2B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CEO / Fondateur</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Logiadapt</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Marseille (13)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,FONDATEUR,5-50,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Poste: Directeur/Directrice Commercial(e) B2B et B2C CDI | Date: NC | Effectif: NC (&lt; 50) | CA: NC | Salaire: 70-80 k EUR (fixe 57-66 k + variable 25% + BSPCE 0|6% du capital) | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/logiadapt/jobs/directeur-ou-directrice-commercial-b2b-et-b2c_marseille | Contexte: Entreprise a impact creee en 2023 (maintien a domicile des seniors| adaptation du logement)| basee a Marseille. Creation du poste de directeur commercial B2B/B2C avec prise de poste annoncee entre juin et septembre 2026 et entree au capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Logiadapt</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Marseille (13)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,5-50,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Poste: Directeur/Directrice Commercial(e) B2B et B2C CDI | Date: NC | Effectif: NC (&lt; 50) | CA: NC | Salaire: 70-80 k EUR (fixe 57-66 k + variable 25% + BSPCE 0|6% du capital) | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/logiadapt/jobs/directeur-ou-directrice-commercial-b2b-et-b2c_marseille | Contexte: Entreprise a impact creee en 2023 (maintien a domicile des seniors| adaptation du logement)| basee a Marseille. Creation du poste de directeur commercial B2B/B2C avec prise de poste annoncee entre juin et septembre 2026 et entree au capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Directeur commercial</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ecov</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bordeaux (33)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,NC,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Nouvelle-Aquitaine et Centre-Val de Loire H/F CDI | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/ecov/jobs/responsable-commercial-nouvelle-aquitaine-et-centre-val-de-loire-h-f_bordeaux | Contexte: Operateur de lignes de covoiturage du quotidien pour les collectivites. Ouverture d'un poste de responsable commercial couvrant Nouvelle-Aquitaine et Centre-Val de Loire base a Bordeaux| avec prospection active aupres des collectivites : signal d'extension de la couverture commerciale regionale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ecov</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bordeaux (33)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,NC,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Nouvelle-Aquitaine et Centre-Val de Loire H/F CDI | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/ecov/jobs/responsable-commercial-nouvelle-aquitaine-et-centre-val-de-loire-h-f_bordeaux | Contexte: Operateur de lignes de covoiturage du quotidien pour les collectivites. Ouverture d'un poste de responsable commercial couvrant Nouvelle-Aquitaine et Centre-Val de Loire base a Bordeaux| avec prospection active aupres des collectivites : signal d'extension de la couverture commerciale regionale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Directeur commercial France</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Clasquin</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Roissy-en-France (95)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,500-2000,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Poste: Key Account Manager / Responsable Grands Comptes H/F CDI | Date: NC | Effectif: NC (env. 1 400) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/clasquin/jobs/key-account-manager-responsable-grands-comptes-h-f_roissy-en-france | Contexte: Commissionnaire de transport et organisateur de transport international independant| siege a Lyon| reseau mondial. Recrute un Key Account Manager grands comptes sur la plateforme de Roissy : renfort de la couverture grands comptes overseas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Clasquin</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Roissy-en-France (95)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,TALENT_ACQUISITION,500-2000,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Poste: Key Account Manager / Responsable Grands Comptes H/F CDI | Date: NC | Effectif: NC (env. 1 400) | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/clasquin/jobs/key-account-manager-responsable-grands-comptes-h-f_roissy-en-france | Contexte: Commissionnaire de transport et organisateur de transport international independant| siege a Lyon| reseau mondial. Recrute un Key Account Manager grands comptes sur la plateforme de Roissy : renfort de la couverture grands comptes overseas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Directeur commercial</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Eres</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Angouleme (16)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DIRECTEUR_COMMERCIAL,50-500,CONTACT_1,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Eres Entreprise (Poitou-Charentes/Centre) H/F CDI | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/eres-group/jobs/responsable-commercial-eres-entreprise-la-rochelle-h-f_toulouse | Contexte: Societe independante specialisee en epargne salariale et retraite d'entreprise. Poste de responsable commercial regional (developpement du reseau de prescripteurs et distribution des offres) avec prise de poste annoncee au 31 aout 2026 : signal d'extension de la force de vente sur Poitou-Charentes / Centre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DRH</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Eres</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Angouleme (16)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>SALES,JOB,DRH,50-500,CONTACT_2,CONTACT_NON_SOURCE</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Poste: Responsable Commercial Eres Entreprise (Poitou-Charentes/Centre) H/F CDI | Date: NC | Effectif: NC | CA: NC | Salaire: NC | Source: Welcome to the Jungle | Lien: https://www.welcometothejungle.com/fr/companies/eres-group/jobs/responsable-commercial-eres-entreprise-la-rochelle-h-f_toulouse | Contexte: Societe independante specialisee en epargne salariale et retraite d'entreprise. Poste de responsable commercial regional (developpement du reseau de prescripteurs et distribution des offres) avec prise de poste annoncee au 31 aout 2026 : signal d'extension de la force de vente sur Poitou-Charentes / Centre.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/humanup_market_mapping_2026-09-03.xlsx
+++ b/outputs/humanup_market_mapping_2026-09-03.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -611,1126 +611,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rapport de synthese</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t># Rapport de Synthèse — Market Mapping Humanup.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>**Date :** 2026-09-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>**Destinataires :** Valentin Murcia (Finance + Hospitality), Alexis (Industrie), Louis (Sales SaaS), Méroë Nguimbi (Sales général)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>## 1. Volumes par vertical</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>| Vertical | Destinataire | Lignes | Entreprises uniques | Contacts sourcés | % sourcé |</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|---|</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>| Finance | Valentin | 38 / 40 | 18 | 5 | 13 % |</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>| Hospitality | Valentin | 40 / 40 | 19 | 3 | 8 % |</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>| Industrie | Alexis | 40 / 40 | 20 | 3 | 8 % |</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>| Sales SaaS | Louis | 40 / 40 | 20 | **20** | **50 %** |</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>| Sales général | Méroë | 40 / 40 | 20 | 3 | 8 % |</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>| **TOTAL** | | **198** | **97** | **34** | **17 %** |</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>**Répartition JOB / NEWS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>| Vertical | JOB | NEWS |</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>| Finance | 29 | 9 |</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>| Hospitality | 28 | 12 |</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>| Industrie | 28 | 12 |</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>| Sales SaaS | 28 | 12 |</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>| Sales général | 40 | 0 |</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>## 2. Top régions / villes / secteurs</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>**Finance** — Paris (75) domine avec 11 lignes, puis Lyon (69) 4, Douarnenez (29) 3, et une</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>diagonale francilienne périphérique (Orly 94, Le Blanc-Mesnil 93, Taverny 95). Secteurs : cabinets</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>d'expertise comptable indépendants en consolidation, ETI familiales industrielles, médico-social.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>**Hospitality** — Paris (75) très majoritaire (18 lignes), Chamonix (74) 4, puis un chapelet</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>d'établissements de province et d'outre-mer : Cognac (16), La Teste-de-Buch (33), Loir-et-Cher (41),</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Polynésie (987). Secteurs : hôtellerie 4-5* indépendante, ouvertures et pré-ouvertures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>**Industrie** — La verticale la plus régionale, conformément à la consigne géographique.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Pays de la Loire en tête : Maine-et-Loire (49) 6 lignes, Vendée (85) 4. Puis Lot (46), Nord (59),</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Haute-Loire (43), Finistère (29). Secteurs : sous-traitance aéronautique, matériaux de construction,</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>électronique industrielle, agroalimentaire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>**Sales SaaS** — Concentration parisienne assumée (75) 28 lignes, Lyon (69) 6, Hauts-de-Seine (92) 4,</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Yvelines (78) 2. Secteurs : SaaS vertical métier (santé au travail, expertise comptable, restauration),</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>deeptech, fintech B2B.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>**Sales général** — La mieux répartie : Marne (51) 4, Bouches-du-Rhône (13) 4, Haute-Garonne (31) 4,</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>puis Rhône (69), Tarn (81), Finistère (29). Secteurs : négoce de matériaux, instrumentation de mesure,</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>services à la personne, distribution B2B.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>## 3. Top 7 signaux business prioritaires</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>1. **MyUnisoft** (Saint-Quentin-en-Yvelines, 253 sal.) — Plan de 100 recrutements sur 2026, soit un</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   passage de 253 à 353 collaborateurs, sous actionnariat majoritaire **HgCapital**. Le meilleur signal</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   du jour : volume, capital patient, éditeur peu médiatisé. → **LOUIS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2. **padoa** (Paris) — **Thoma Bravo** prend le majoritaire via son fonds Europe de 1,8 Md€ ;</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Five Arrows et Kamet réinvestissent. Plan d'expansion DACH annoncé, donc recrutements commerciaux</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   à venir. → **LOUIS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>3. **Groupe Derrey** (Étival-Clairefontaine, 88, 600 sal.) — Campagne de 26 postes en CDI dans le</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Grand Est, dont plusieurs profils commerce ; annonce technico-commercial ouverte à Épinal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Négociant en matériaux indépendant, exactement notre cible. → **MÉROË**</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>4. **N2JSoft / N2F** (Lyon, 70 → 130 sal. en un an, &gt; 10 M€ de CA) — Recrute simultanément</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Sales Enablement Manager, RevOps Manager et SDR : refonte complète de la machine commerciale</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   d'un éditeur indépendant et discret. → **LOUIS**</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>5. **FDG Group** (Orly, 94, 630 sal., 117 M€ de CA) — Deux postes de contrôle de gestion ouverts en</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   parallèle (business partner opérationnel + corporate) : renforcement net et simultané de l'équipe</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   CDG, signal classique de structuration. → **VALENTIN**</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>6. **Chauvin Arnoux** (instrumentation de mesure, groupe familial indépendant, 430 sal., 57 M€) —</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Création d'un poste d'ingénieur technico-commercial itinérant sur la zone Toulouse : ouverture de</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   territoire, pas un remplacement. → **MÉROË**</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>7. **Techmo Hygiène** (Le Blanc-Mesnil, 93, 280 sal., groupe familial indépendant depuis 1947) —</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Comptable général expérimenté avec encadrement de deux comptables fournisseurs : structuration de</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   la fonction comptable dans une PME patrimoniale. → **VALENTIN**</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>## 4. Récurrences</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Périmètre scanné : **172 entreprises** déjà ciblées par les fichiers des 01/09, 02/09 et 03/09.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Ces entreprises sont exclues de la nouvelle recherche, mais vérifiées pour signal frais (27/08 → 03/09).</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>**3 récurrences confirmées :**</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>- **Figeac Aéro** (aéronautique / défense) — Chiffre d'affaires T1 2026/27 à 111,8 M€, 21e trimestre</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  consécutif de croissance (+11,6 % organique), carnet de commandes record à 5 Md€ — 02/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Signal de croissance soutenue, angle Industrie et Finance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>- **Voyageurs du Monde** (tourisme sur mesure) — AVANTAGE (86,59 % du capital) annonce une offre</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  publique de retrait à 180 € par action et la sortie de cote d'Euronext Paris — 01/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Sortie de cote : réorganisation probable des fonctions support, angle Finance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>- **STIF** (industrie, sécurité explosion et stockage d'énergie) — Déclaration mensuelle de droits de</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  vote au 31/08 — 02/09/2026. Signal réglementaire de routine, **faible valeur commerciale**.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Le détail, y compris les pistes écartées faute de datation dans la fenêtre, est dans</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>`outputs/_recurrences_2026-09-03.md`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>## 5. Filtres appliqués</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>**Liste noire** — appliquée aux cinq verticales : Big 4, next tier (Mazars, Grant Thornton, BDO, RSM,</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Baker Tilly), réseaux d'expertise comptable (In Extenso, Fiducial, Cerfrance, Exco, Sofarec),</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>scale-ups surmédiatisées, CAC 40, et cabinets d'intérim masquant le client final.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>**Plafond 2000 salariés au niveau groupe** — exclusions prononcées aujourd'hui :</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Padam Mobility (filiale Siemens Mobility), Mabéo Industries (groupe Martin Belaysoud),</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Fnac Darty, Primagaz, Jacquet Brossard, Agicap (FT120, trop visible).</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Intermédiaires écartés pour employeur final masqué : Dream Catcher Sales, Tomcat Talents, Jobglober.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Écartés faute d'effectif vérifiable : Nopillo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>**Alternance / stage** — zéro annonce en alternance, apprentissage, contrat pro ou stage dans les</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>fichiers livrés. Wimi a été écarté à ce titre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>**Anti-doublons 14 jours** — les 172 entreprises déjà ciblées sont absentes des cinq fichiers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>## 6. Dédoublonnage Sales</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Le fichier de Méroë a été confronté au fichier de Louis sur la colonne `entreprise` :</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>**aucune entreprise retirée**, les deux agents ayant travaillé sur des périmètres disjoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>(l'agent Sales général avait pour consigne d'éviter les éditeurs SaaS et tech B2B).</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Les deux fichiers sortent donc à 40 lignes pleines, 20 entreprises chacun, sans recouvrement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>## 7. Limites du run — à lire</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Ce run mérite trois réserves explicites.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>**Contacts non sourcés.** Sur 198 lignes, 34 seulement portent un nom. Le budget de recherche web de</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>la session (200 requêtes, partagé entre tous les agents) a été épuisé avant la phase de sourcing</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>nominatif sur quatre verticales sur cinq. Seul le fichier Sales SaaS de Louis atteint 50 % de contacts</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>nommés. **Aucun nom n'a été inventé** : les lignes non sourcées portent le tag `CONTACT_NON_SOURCE`</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>et des colonnes `nom` / `prenom` / `linkedin` vides, à enrichir via FullEnrich ou une session dédiée.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>**Dates de publication majoritairement en `NC`.** Le proxy de cet environnement bloque en accès direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>la quasi-totalité des sources utiles — APEC, Indeed, Hellowork, LinkedIn, Welcome to the Jungle,</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>France Travail, Pappers, Societe.com, ainsi que la plupart des sites carrière. Le travail s'est fait</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>sur les extraits de résultats de recherche. Les annonces retenues sont des offres réellement en ligne</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>au 03/09/2026 à employeur nommé, mais la fenêtre « publiée dans les 7 derniers jours » n'est pas</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>confirmable pour la majorité d'entre elles. Chaque ligne porte sa date réelle ou `NC` dans les notes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>**Deux écarts de volume assumés.** Finance sort à 38 lignes au lieu de 40 (la partie A, comptabilité</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>générale et contrôle de gestion, n'a pas trouvé une cinquième opportunité vérifiable). Sales général</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>sort à 40 lignes mais avec 40 JOB et 0 NEWS : toutes les pistes NEWS remontées ont été écartées après</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>vérification — dates réelles hors fenêtre (Partedis, FATEC Group, Aditec) ou effectif groupe au-dessus</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>du plafond. Aucun signal n'a été fabriqué pour combler le quota.</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>## 8. Fichiers livrés</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>| Fichier | Lignes | Destinataire |</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>| `outputs/finance_2026-09-03.csv` | 38 | Valentin Murcia |</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>| `outputs/hospitality_2026-09-03.csv` | 40 | Valentin Murcia |</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>| `outputs/industrie_2026-09-03.csv` | 40 | Alexis |</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>| `outputs/sales_saas_2026-09-03.csv` | 40 | Louis |</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>| `outputs/sales_2026-09-03.csv` | 40 | Méroë Nguimbi |</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>| `outputs/humanup_market_mapping_2026-09-03.xlsx` | 6 onglets | Méroë Nguimbi |</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>| `outputs/rapport_synthese_2026-09-03.md` | — | Méroë Nguimbi |</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Fichiers intermédiaires conservés pour traçabilité : `_fin_a`, `_fin_a_complement`, `_fin_b`,</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>`_fin_c`, `_sales_complement`, `_recurrences`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>## 9. Actions prioritaires</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>1. **Attaquer MyUnisoft et padoa aujourd'hui** (Louis). Ce sont les deux signaux les plus chauds du</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   jour et les seuls adossés à un fonds avec un plan de recrutement explicite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>2. **Lancer l'enrichissement FullEnrich** sur les 164 lignes `CONTACT_NON_SOURCE` avant toute</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   séquence d'approche : les fichiers Finance, Hospitality, Industrie et Sales général sont</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   inexploitables en l'état sans noms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>3. **Groupe Derrey** (Méroë) : 26 postes ouverts d'un coup chez un négociant indépendant de 600</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   salariés, c'est un mandat multi-postes potentiel, pas une mission unitaire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>4. **Requalifier les dates** des annonces marquées `NC` avant approche, depuis un poste ayant accès</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   à l'APEC et à LinkedIn : une annonce de plus de trois semaines change l'angle d'appel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>5. **Prévoir une session de sourcing dédiée** avec budget de recherche réservé, pour ne pas</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   reproduire l'épuisement constaté sur ce run.</t>
+          <t>Rapport de synthese complet : outputs/rapport_synthese_2026-09-03.md</t>
         </is>
       </c>
     </row>
